--- a/data_promo_eligible.xlsx
+++ b/data_promo_eligible.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dashboard\Analisa_Promo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{531F3E74-A0C7-4B74-AE0F-88B8FEC15860}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2DD6CB6B-09CB-45DB-9BD5-232D629A974C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{DF736937-0333-4947-9A5F-39FAA35E4834}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="data_promo_eligible" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">data_promo_eligible!$A$1:$L$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">data_promo_eligible!$A$1:$L$2556</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14154" uniqueCount="154">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15342" uniqueCount="163">
   <si>
     <t>customer_id</t>
   </si>
@@ -505,6 +505,33 @@
   <si>
     <t>b. 4-6 Months</t>
   </si>
+  <si>
+    <t xml:space="preserve">Promo Loyalty Customer 2026 + Discount 30% - 1 Months  </t>
+  </si>
+  <si>
+    <t>Promo Loyalty Customer 2026 - Bill in Advance Pay 12 Get 18</t>
+  </si>
+  <si>
+    <t>Promo Loyalty Counter ISP MV - Speedboost + Discount 12 Months</t>
+  </si>
+  <si>
+    <t>Regular Promo Maret 2025 - Golf Island Area - Bill in Advance Pay 6 Get 7</t>
+  </si>
+  <si>
+    <t>Promo Loyalty Customer 2026 - Bill in Advance Pay 6 Get 9</t>
+  </si>
+  <si>
+    <t>Subang</t>
+  </si>
+  <si>
+    <t>Maros</t>
+  </si>
+  <si>
+    <t>Karanganyar</t>
+  </si>
+  <si>
+    <t>Grace Alexandra</t>
+  </si>
 </sst>
 </file>
 
@@ -896,7 +923,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{129E8E4B-63D9-47F0-9896-1DD628D404DA}">
-  <dimension ref="A1:P2366"/>
+  <dimension ref="A1:P2556"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.140625" bestFit="1" customWidth="1"/>
@@ -90524,39 +90551,7530 @@
       </c>
     </row>
     <row r="2359" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="K2359" s="2"/>
-      <c r="L2359" s="2"/>
+      <c r="A2359">
+        <v>45404286</v>
+      </c>
+      <c r="B2359" s="5">
+        <v>46251</v>
+      </c>
+      <c r="C2359" t="s">
+        <v>142</v>
+      </c>
+      <c r="D2359" s="5">
+        <v>45764</v>
+      </c>
+      <c r="E2359" t="s">
+        <v>150</v>
+      </c>
+      <c r="F2359" t="s">
+        <v>31</v>
+      </c>
+      <c r="G2359" t="s">
+        <v>32</v>
+      </c>
+      <c r="H2359" t="s">
+        <v>67</v>
+      </c>
+      <c r="I2359" t="s">
+        <v>65</v>
+      </c>
+      <c r="J2359" s="5">
+        <v>46248.331250000003</v>
+      </c>
+      <c r="K2359" s="2">
+        <v>8</v>
+      </c>
+      <c r="L2359" s="2">
+        <v>2026</v>
+      </c>
     </row>
     <row r="2360" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="K2360" s="2"/>
-      <c r="L2360" s="2"/>
+      <c r="A2360">
+        <v>35232054</v>
+      </c>
+      <c r="B2360" s="5">
+        <v>46240</v>
+      </c>
+      <c r="C2360" t="s">
+        <v>62</v>
+      </c>
+      <c r="D2360" s="5">
+        <v>45906</v>
+      </c>
+      <c r="E2360" t="s">
+        <v>152</v>
+      </c>
+      <c r="F2360" t="s">
+        <v>31</v>
+      </c>
+      <c r="G2360" t="s">
+        <v>40</v>
+      </c>
+      <c r="H2360" t="s">
+        <v>41</v>
+      </c>
+      <c r="I2360" t="s">
+        <v>65</v>
+      </c>
+      <c r="J2360" s="5">
+        <v>46244.34375</v>
+      </c>
+      <c r="K2360" s="2">
+        <v>8</v>
+      </c>
+      <c r="L2360" s="2">
+        <v>2026</v>
+      </c>
     </row>
     <row r="2361" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="K2361" s="2"/>
-      <c r="L2361" s="2"/>
+      <c r="A2361">
+        <v>30186496</v>
+      </c>
+      <c r="B2361" s="5">
+        <v>46235</v>
+      </c>
+      <c r="C2361" t="s">
+        <v>62</v>
+      </c>
+      <c r="D2361" s="5">
+        <v>46053</v>
+      </c>
+      <c r="E2361" t="s">
+        <v>151</v>
+      </c>
+      <c r="F2361" t="s">
+        <v>11</v>
+      </c>
+      <c r="G2361" t="s">
+        <v>49</v>
+      </c>
+      <c r="H2361" t="s">
+        <v>50</v>
+      </c>
+      <c r="I2361" t="s">
+        <v>65</v>
+      </c>
+      <c r="J2361" s="5">
+        <v>46238.343055555553</v>
+      </c>
+      <c r="K2361" s="2">
+        <v>8</v>
+      </c>
+      <c r="L2361" s="2">
+        <v>2026</v>
+      </c>
     </row>
     <row r="2362" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="K2362" s="2"/>
-      <c r="L2362" s="2"/>
+      <c r="A2362">
+        <v>20169644</v>
+      </c>
+      <c r="B2362" s="5">
+        <v>46238</v>
+      </c>
+      <c r="C2362" t="s">
+        <v>144</v>
+      </c>
+      <c r="D2362" s="5">
+        <v>45842</v>
+      </c>
+      <c r="E2362" t="s">
+        <v>150</v>
+      </c>
+      <c r="F2362" t="s">
+        <v>16</v>
+      </c>
+      <c r="G2362" t="s">
+        <v>20</v>
+      </c>
+      <c r="H2362" t="s">
+        <v>21</v>
+      </c>
+      <c r="I2362" t="s">
+        <v>65</v>
+      </c>
+      <c r="J2362" s="5">
+        <v>46244.348611111112</v>
+      </c>
+      <c r="K2362" s="2">
+        <v>8</v>
+      </c>
+      <c r="L2362" s="2">
+        <v>2026</v>
+      </c>
     </row>
     <row r="2363" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="K2363" s="2"/>
-      <c r="L2363" s="2"/>
+      <c r="A2363">
+        <v>20196048</v>
+      </c>
+      <c r="B2363" s="5">
+        <v>46247</v>
+      </c>
+      <c r="C2363" t="s">
+        <v>144</v>
+      </c>
+      <c r="D2363" s="5">
+        <v>46035</v>
+      </c>
+      <c r="E2363" t="s">
+        <v>151</v>
+      </c>
+      <c r="F2363" t="s">
+        <v>16</v>
+      </c>
+      <c r="G2363" t="s">
+        <v>20</v>
+      </c>
+      <c r="H2363" t="s">
+        <v>21</v>
+      </c>
+      <c r="I2363" t="s">
+        <v>65</v>
+      </c>
+      <c r="J2363" s="5">
+        <v>46252.31527777778</v>
+      </c>
+      <c r="K2363" s="2">
+        <v>8</v>
+      </c>
+      <c r="L2363" s="2">
+        <v>2026</v>
+      </c>
     </row>
     <row r="2364" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="K2364" s="2"/>
-      <c r="L2364" s="2"/>
+      <c r="A2364">
+        <v>20213874</v>
+      </c>
+      <c r="B2364" s="5">
+        <v>46238</v>
+      </c>
+      <c r="C2364" t="s">
+        <v>103</v>
+      </c>
+      <c r="D2364" s="5">
+        <v>46177</v>
+      </c>
+      <c r="E2364" t="s">
+        <v>148</v>
+      </c>
+      <c r="F2364" t="s">
+        <v>16</v>
+      </c>
+      <c r="G2364" t="s">
+        <v>20</v>
+      </c>
+      <c r="H2364" t="s">
+        <v>57</v>
+      </c>
+      <c r="I2364" t="s">
+        <v>65</v>
+      </c>
+      <c r="J2364" s="5">
+        <v>46246.62777777778</v>
+      </c>
+      <c r="K2364" s="2">
+        <v>8</v>
+      </c>
+      <c r="L2364" s="2">
+        <v>2026</v>
+      </c>
     </row>
     <row r="2365" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="K2365" s="2"/>
-      <c r="L2365" s="2"/>
+      <c r="A2365">
+        <v>22005759</v>
+      </c>
+      <c r="B2365" s="5">
+        <v>46238</v>
+      </c>
+      <c r="C2365" t="s">
+        <v>103</v>
+      </c>
+      <c r="D2365" s="5">
+        <v>46057</v>
+      </c>
+      <c r="E2365" t="s">
+        <v>151</v>
+      </c>
+      <c r="F2365" t="s">
+        <v>16</v>
+      </c>
+      <c r="G2365" t="s">
+        <v>100</v>
+      </c>
+      <c r="H2365" t="s">
+        <v>111</v>
+      </c>
+      <c r="I2365" t="s">
+        <v>65</v>
+      </c>
+      <c r="J2365" s="5">
+        <v>46244.326388888891</v>
+      </c>
+      <c r="K2365" s="2">
+        <v>8</v>
+      </c>
+      <c r="L2365" s="2">
+        <v>2026</v>
+      </c>
     </row>
     <row r="2366" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="K2366" s="2"/>
-      <c r="L2366" s="2"/>
+      <c r="A2366">
+        <v>21121867</v>
+      </c>
+      <c r="B2366" s="5">
+        <v>46235</v>
+      </c>
+      <c r="C2366" t="s">
+        <v>23</v>
+      </c>
+      <c r="D2366" s="5">
+        <v>45625</v>
+      </c>
+      <c r="E2366" t="s">
+        <v>150</v>
+      </c>
+      <c r="F2366" t="s">
+        <v>16</v>
+      </c>
+      <c r="G2366" t="s">
+        <v>54</v>
+      </c>
+      <c r="H2366" t="s">
+        <v>55</v>
+      </c>
+      <c r="I2366" t="s">
+        <v>65</v>
+      </c>
+      <c r="J2366" s="5">
+        <v>46239.372916666667</v>
+      </c>
+      <c r="K2366">
+        <v>8</v>
+      </c>
+      <c r="L2366">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2367" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2367">
+        <v>21158546</v>
+      </c>
+      <c r="B2367" s="5">
+        <v>46241</v>
+      </c>
+      <c r="C2367" t="s">
+        <v>103</v>
+      </c>
+      <c r="D2367" s="5">
+        <v>46088</v>
+      </c>
+      <c r="E2367" t="s">
+        <v>153</v>
+      </c>
+      <c r="F2367" t="s">
+        <v>16</v>
+      </c>
+      <c r="G2367" t="s">
+        <v>54</v>
+      </c>
+      <c r="H2367" t="s">
+        <v>55</v>
+      </c>
+      <c r="I2367" t="s">
+        <v>65</v>
+      </c>
+      <c r="J2367" s="5">
+        <v>46246.365277777775</v>
+      </c>
+      <c r="K2367">
+        <v>8</v>
+      </c>
+      <c r="L2367">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2368" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2368">
+        <v>21162232</v>
+      </c>
+      <c r="B2368" s="5">
+        <v>46240</v>
+      </c>
+      <c r="C2368" t="s">
+        <v>103</v>
+      </c>
+      <c r="D2368" s="5">
+        <v>46148</v>
+      </c>
+      <c r="E2368" t="s">
+        <v>153</v>
+      </c>
+      <c r="F2368" t="s">
+        <v>16</v>
+      </c>
+      <c r="G2368" t="s">
+        <v>54</v>
+      </c>
+      <c r="H2368" t="s">
+        <v>55</v>
+      </c>
+      <c r="I2368" t="s">
+        <v>65</v>
+      </c>
+      <c r="J2368" s="5">
+        <v>46244.331944444442</v>
+      </c>
+      <c r="K2368">
+        <v>8</v>
+      </c>
+      <c r="L2368">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2369" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2369">
+        <v>45319731</v>
+      </c>
+      <c r="B2369" s="5">
+        <v>46238</v>
+      </c>
+      <c r="C2369" t="s">
+        <v>142</v>
+      </c>
+      <c r="D2369" s="5">
+        <v>44777</v>
+      </c>
+      <c r="E2369" t="s">
+        <v>149</v>
+      </c>
+      <c r="F2369" t="s">
+        <v>31</v>
+      </c>
+      <c r="G2369" t="s">
+        <v>32</v>
+      </c>
+      <c r="H2369" t="s">
+        <v>37</v>
+      </c>
+      <c r="I2369" t="s">
+        <v>59</v>
+      </c>
+      <c r="J2369" s="5">
+        <v>46242.48541666667</v>
+      </c>
+      <c r="K2369">
+        <v>8</v>
+      </c>
+      <c r="L2369">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2370" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2370">
+        <v>45376244</v>
+      </c>
+      <c r="B2370" s="5">
+        <v>46240</v>
+      </c>
+      <c r="C2370" t="s">
+        <v>62</v>
+      </c>
+      <c r="D2370" s="5">
+        <v>45875</v>
+      </c>
+      <c r="E2370" t="s">
+        <v>150</v>
+      </c>
+      <c r="F2370" t="s">
+        <v>31</v>
+      </c>
+      <c r="G2370" t="s">
+        <v>32</v>
+      </c>
+      <c r="H2370" t="s">
+        <v>33</v>
+      </c>
+      <c r="I2370" t="s">
+        <v>59</v>
+      </c>
+      <c r="J2370" s="5">
+        <v>46242.490972222222</v>
+      </c>
+      <c r="K2370">
+        <v>8</v>
+      </c>
+      <c r="L2370">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2371" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2371">
+        <v>45412900</v>
+      </c>
+      <c r="B2371" s="5">
+        <v>46241</v>
+      </c>
+      <c r="C2371" t="s">
+        <v>62</v>
+      </c>
+      <c r="D2371" s="5">
+        <v>45876</v>
+      </c>
+      <c r="E2371" t="s">
+        <v>150</v>
+      </c>
+      <c r="F2371" t="s">
+        <v>31</v>
+      </c>
+      <c r="G2371" t="s">
+        <v>32</v>
+      </c>
+      <c r="H2371" t="s">
+        <v>93</v>
+      </c>
+      <c r="I2371" t="s">
+        <v>59</v>
+      </c>
+      <c r="J2371" s="5">
+        <v>46246.626388888886</v>
+      </c>
+      <c r="K2371">
+        <v>8</v>
+      </c>
+      <c r="L2371">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2372" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2372">
+        <v>35220069</v>
+      </c>
+      <c r="B2372" s="5">
+        <v>46243</v>
+      </c>
+      <c r="C2372" t="s">
+        <v>145</v>
+      </c>
+      <c r="D2372" s="5">
+        <v>45756</v>
+      </c>
+      <c r="E2372" t="s">
+        <v>150</v>
+      </c>
+      <c r="F2372" t="s">
+        <v>31</v>
+      </c>
+      <c r="G2372" t="s">
+        <v>40</v>
+      </c>
+      <c r="H2372" t="s">
+        <v>72</v>
+      </c>
+      <c r="I2372" t="s">
+        <v>59</v>
+      </c>
+      <c r="J2372" s="5">
+        <v>46246.632638888892</v>
+      </c>
+      <c r="K2372">
+        <v>8</v>
+      </c>
+      <c r="L2372">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2373" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2373">
+        <v>20147630</v>
+      </c>
+      <c r="B2373" s="5">
+        <v>46240</v>
+      </c>
+      <c r="C2373" t="s">
+        <v>144</v>
+      </c>
+      <c r="D2373" s="5">
+        <v>45967</v>
+      </c>
+      <c r="E2373" t="s">
+        <v>152</v>
+      </c>
+      <c r="F2373" t="s">
+        <v>16</v>
+      </c>
+      <c r="G2373" t="s">
+        <v>20</v>
+      </c>
+      <c r="H2373" t="s">
+        <v>21</v>
+      </c>
+      <c r="I2373" t="s">
+        <v>59</v>
+      </c>
+      <c r="J2373" s="5">
+        <v>46246.62222222222</v>
+      </c>
+      <c r="K2373">
+        <v>8</v>
+      </c>
+      <c r="L2373">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2374" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2374">
+        <v>20169404</v>
+      </c>
+      <c r="B2374" s="5">
+        <v>46237</v>
+      </c>
+      <c r="C2374" t="s">
+        <v>62</v>
+      </c>
+      <c r="D2374" s="5">
+        <v>45841</v>
+      </c>
+      <c r="E2374" t="s">
+        <v>150</v>
+      </c>
+      <c r="F2374" t="s">
+        <v>16</v>
+      </c>
+      <c r="G2374" t="s">
+        <v>20</v>
+      </c>
+      <c r="H2374" t="s">
+        <v>21</v>
+      </c>
+      <c r="I2374" t="s">
+        <v>59</v>
+      </c>
+      <c r="J2374" s="5">
+        <v>46240.369444444441</v>
+      </c>
+      <c r="K2374">
+        <v>8</v>
+      </c>
+      <c r="L2374">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2375" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2375">
+        <v>21125248</v>
+      </c>
+      <c r="B2375" s="5">
+        <v>46244</v>
+      </c>
+      <c r="C2375" t="s">
+        <v>62</v>
+      </c>
+      <c r="D2375" s="5">
+        <v>45667</v>
+      </c>
+      <c r="E2375" t="s">
+        <v>150</v>
+      </c>
+      <c r="F2375" t="s">
+        <v>16</v>
+      </c>
+      <c r="G2375" t="s">
+        <v>54</v>
+      </c>
+      <c r="H2375" t="s">
+        <v>78</v>
+      </c>
+      <c r="I2375" t="s">
+        <v>59</v>
+      </c>
+      <c r="J2375" s="5">
+        <v>46251.637499999997</v>
+      </c>
+      <c r="K2375">
+        <v>8</v>
+      </c>
+      <c r="L2375">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2376" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2376">
+        <v>21160505</v>
+      </c>
+      <c r="B2376" s="5">
+        <v>46243</v>
+      </c>
+      <c r="C2376" t="s">
+        <v>103</v>
+      </c>
+      <c r="D2376" s="5">
+        <v>46121</v>
+      </c>
+      <c r="E2376" t="s">
+        <v>153</v>
+      </c>
+      <c r="F2376" t="s">
+        <v>16</v>
+      </c>
+      <c r="G2376" t="s">
+        <v>54</v>
+      </c>
+      <c r="H2376" t="s">
+        <v>55</v>
+      </c>
+      <c r="I2376" t="s">
+        <v>59</v>
+      </c>
+      <c r="J2376" s="5">
+        <v>46246.629861111112</v>
+      </c>
+      <c r="K2376">
+        <v>8</v>
+      </c>
+      <c r="L2376">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2377" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2377">
+        <v>33030441</v>
+      </c>
+      <c r="B2377" s="5">
+        <v>46244</v>
+      </c>
+      <c r="C2377" t="s">
+        <v>62</v>
+      </c>
+      <c r="D2377" s="5">
+        <v>46001</v>
+      </c>
+      <c r="E2377" t="s">
+        <v>151</v>
+      </c>
+      <c r="F2377" t="s">
+        <v>31</v>
+      </c>
+      <c r="G2377" t="s">
+        <v>95</v>
+      </c>
+      <c r="H2377" t="s">
+        <v>97</v>
+      </c>
+      <c r="I2377" t="s">
+        <v>59</v>
+      </c>
+      <c r="J2377" s="5">
+        <v>46251.652083333334</v>
+      </c>
+      <c r="K2377">
+        <v>8</v>
+      </c>
+      <c r="L2377">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2378" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2378">
+        <v>20211918</v>
+      </c>
+      <c r="B2378" s="5">
+        <v>46243</v>
+      </c>
+      <c r="C2378" t="s">
+        <v>103</v>
+      </c>
+      <c r="D2378" s="5">
+        <v>46151</v>
+      </c>
+      <c r="E2378" t="s">
+        <v>153</v>
+      </c>
+      <c r="F2378" t="s">
+        <v>16</v>
+      </c>
+      <c r="G2378" t="s">
+        <v>20</v>
+      </c>
+      <c r="H2378" t="s">
+        <v>21</v>
+      </c>
+      <c r="I2378" t="s">
+        <v>88</v>
+      </c>
+      <c r="J2378" s="5">
+        <v>46252.353472222225</v>
+      </c>
+      <c r="K2378">
+        <v>8</v>
+      </c>
+      <c r="L2378">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2379" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2379">
+        <v>21076186</v>
+      </c>
+      <c r="B2379" s="5">
+        <v>46238</v>
+      </c>
+      <c r="C2379" t="s">
+        <v>158</v>
+      </c>
+      <c r="D2379" s="5">
+        <v>44565</v>
+      </c>
+      <c r="E2379" t="s">
+        <v>149</v>
+      </c>
+      <c r="F2379" t="s">
+        <v>16</v>
+      </c>
+      <c r="G2379" t="s">
+        <v>54</v>
+      </c>
+      <c r="H2379" t="s">
+        <v>55</v>
+      </c>
+      <c r="I2379" t="s">
+        <v>88</v>
+      </c>
+      <c r="J2379" s="5">
+        <v>46241.466666666667</v>
+      </c>
+      <c r="K2379">
+        <v>8</v>
+      </c>
+      <c r="L2379">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2380" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2380">
+        <v>21158199</v>
+      </c>
+      <c r="B2380" s="5">
+        <v>46236</v>
+      </c>
+      <c r="C2380" t="s">
+        <v>103</v>
+      </c>
+      <c r="D2380" s="5">
+        <v>46083</v>
+      </c>
+      <c r="E2380" t="s">
+        <v>153</v>
+      </c>
+      <c r="F2380" t="s">
+        <v>16</v>
+      </c>
+      <c r="G2380" t="s">
+        <v>54</v>
+      </c>
+      <c r="H2380" t="s">
+        <v>55</v>
+      </c>
+      <c r="I2380" t="s">
+        <v>88</v>
+      </c>
+      <c r="J2380" s="5">
+        <v>46238.352777777778</v>
+      </c>
+      <c r="K2380">
+        <v>8</v>
+      </c>
+      <c r="L2380">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2381" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2381">
+        <v>31192458</v>
+      </c>
+      <c r="B2381" s="5">
+        <v>46241</v>
+      </c>
+      <c r="C2381" t="s">
+        <v>103</v>
+      </c>
+      <c r="D2381" s="5">
+        <v>46060</v>
+      </c>
+      <c r="E2381" t="s">
+        <v>151</v>
+      </c>
+      <c r="F2381" t="s">
+        <v>31</v>
+      </c>
+      <c r="G2381" t="s">
+        <v>45</v>
+      </c>
+      <c r="H2381" t="s">
+        <v>75</v>
+      </c>
+      <c r="I2381" t="s">
+        <v>88</v>
+      </c>
+      <c r="J2381" s="5">
+        <v>46246.622916666667</v>
+      </c>
+      <c r="K2381">
+        <v>8</v>
+      </c>
+      <c r="L2381">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2382" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2382">
+        <v>45421550</v>
+      </c>
+      <c r="B2382" s="5">
+        <v>46243</v>
+      </c>
+      <c r="C2382" t="s">
+        <v>62</v>
+      </c>
+      <c r="D2382" s="5">
+        <v>46000</v>
+      </c>
+      <c r="E2382" t="s">
+        <v>151</v>
+      </c>
+      <c r="F2382" t="s">
+        <v>31</v>
+      </c>
+      <c r="G2382" t="s">
+        <v>32</v>
+      </c>
+      <c r="H2382" t="s">
+        <v>93</v>
+      </c>
+      <c r="I2382" t="s">
+        <v>26</v>
+      </c>
+      <c r="J2382" s="5">
+        <v>46251.355555555558</v>
+      </c>
+      <c r="K2382">
+        <v>8</v>
+      </c>
+      <c r="L2382">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2383" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2383">
+        <v>35217682</v>
+      </c>
+      <c r="B2383" s="5">
+        <v>46236</v>
+      </c>
+      <c r="C2383" t="s">
+        <v>23</v>
+      </c>
+      <c r="D2383" s="5">
+        <v>45718</v>
+      </c>
+      <c r="E2383" t="s">
+        <v>150</v>
+      </c>
+      <c r="F2383" t="s">
+        <v>31</v>
+      </c>
+      <c r="G2383" t="s">
+        <v>40</v>
+      </c>
+      <c r="H2383" t="s">
+        <v>41</v>
+      </c>
+      <c r="I2383" t="s">
+        <v>26</v>
+      </c>
+      <c r="J2383" s="5">
+        <v>46239.373611111114</v>
+      </c>
+      <c r="K2383">
+        <v>8</v>
+      </c>
+      <c r="L2383">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2384" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2384">
+        <v>35238203</v>
+      </c>
+      <c r="B2384" s="5">
+        <v>46235</v>
+      </c>
+      <c r="C2384" t="s">
+        <v>145</v>
+      </c>
+      <c r="D2384" s="5">
+        <v>45991</v>
+      </c>
+      <c r="E2384" t="s">
+        <v>151</v>
+      </c>
+      <c r="F2384" t="s">
+        <v>31</v>
+      </c>
+      <c r="G2384" t="s">
+        <v>40</v>
+      </c>
+      <c r="H2384" t="s">
+        <v>94</v>
+      </c>
+      <c r="I2384" t="s">
+        <v>26</v>
+      </c>
+      <c r="J2384" s="5">
+        <v>46239.381249999999</v>
+      </c>
+      <c r="K2384">
+        <v>8</v>
+      </c>
+      <c r="L2384">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2385" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2385">
+        <v>30163426</v>
+      </c>
+      <c r="B2385" s="5">
+        <v>46243</v>
+      </c>
+      <c r="C2385" t="s">
+        <v>23</v>
+      </c>
+      <c r="D2385" s="5">
+        <v>45697</v>
+      </c>
+      <c r="E2385" t="s">
+        <v>150</v>
+      </c>
+      <c r="F2385" t="s">
+        <v>11</v>
+      </c>
+      <c r="G2385" t="s">
+        <v>49</v>
+      </c>
+      <c r="H2385" t="s">
+        <v>50</v>
+      </c>
+      <c r="I2385" t="s">
+        <v>26</v>
+      </c>
+      <c r="J2385" s="5">
+        <v>46245.375694444447</v>
+      </c>
+      <c r="K2385">
+        <v>8</v>
+      </c>
+      <c r="L2385">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2386" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2386">
+        <v>30188233</v>
+      </c>
+      <c r="B2386" s="5">
+        <v>46237</v>
+      </c>
+      <c r="C2386" t="s">
+        <v>103</v>
+      </c>
+      <c r="D2386" s="5">
+        <v>46084</v>
+      </c>
+      <c r="E2386" t="s">
+        <v>153</v>
+      </c>
+      <c r="F2386" t="s">
+        <v>11</v>
+      </c>
+      <c r="G2386" t="s">
+        <v>49</v>
+      </c>
+      <c r="H2386" t="s">
+        <v>50</v>
+      </c>
+      <c r="I2386" t="s">
+        <v>26</v>
+      </c>
+      <c r="J2386" s="5">
+        <v>46251.367361111108</v>
+      </c>
+      <c r="K2386">
+        <v>8</v>
+      </c>
+      <c r="L2386">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2387" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2387">
+        <v>20182802</v>
+      </c>
+      <c r="B2387" s="5">
+        <v>46247</v>
+      </c>
+      <c r="C2387" t="s">
+        <v>144</v>
+      </c>
+      <c r="D2387" s="5">
+        <v>45943</v>
+      </c>
+      <c r="E2387" t="s">
+        <v>152</v>
+      </c>
+      <c r="F2387" t="s">
+        <v>16</v>
+      </c>
+      <c r="G2387" t="s">
+        <v>20</v>
+      </c>
+      <c r="H2387" t="s">
+        <v>57</v>
+      </c>
+      <c r="I2387" t="s">
+        <v>26</v>
+      </c>
+      <c r="J2387" s="5">
+        <v>46252.43472222222</v>
+      </c>
+      <c r="K2387">
+        <v>8</v>
+      </c>
+      <c r="L2387">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2388" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2388">
+        <v>60007075</v>
+      </c>
+      <c r="B2388" s="5">
+        <v>46243</v>
+      </c>
+      <c r="C2388" t="s">
+        <v>23</v>
+      </c>
+      <c r="D2388" s="5">
+        <v>45756</v>
+      </c>
+      <c r="E2388" t="s">
+        <v>150</v>
+      </c>
+      <c r="F2388" t="s">
+        <v>31</v>
+      </c>
+      <c r="G2388" t="s">
+        <v>63</v>
+      </c>
+      <c r="H2388" t="s">
+        <v>89</v>
+      </c>
+      <c r="I2388" t="s">
+        <v>26</v>
+      </c>
+      <c r="J2388" s="5">
+        <v>46251.361805555556</v>
+      </c>
+      <c r="K2388">
+        <v>8</v>
+      </c>
+      <c r="L2388">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2389" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2389">
+        <v>22005096</v>
+      </c>
+      <c r="B2389" s="5">
+        <v>46240</v>
+      </c>
+      <c r="C2389" t="s">
+        <v>103</v>
+      </c>
+      <c r="D2389" s="5">
+        <v>46028</v>
+      </c>
+      <c r="E2389" t="s">
+        <v>151</v>
+      </c>
+      <c r="F2389" t="s">
+        <v>16</v>
+      </c>
+      <c r="G2389" t="s">
+        <v>100</v>
+      </c>
+      <c r="H2389" t="s">
+        <v>111</v>
+      </c>
+      <c r="I2389" t="s">
+        <v>26</v>
+      </c>
+      <c r="J2389" s="5">
+        <v>46242.393750000003</v>
+      </c>
+      <c r="K2389">
+        <v>8</v>
+      </c>
+      <c r="L2389">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2390" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2390">
+        <v>21127870</v>
+      </c>
+      <c r="B2390" s="5">
+        <v>46238</v>
+      </c>
+      <c r="C2390" t="s">
+        <v>105</v>
+      </c>
+      <c r="D2390" s="5">
+        <v>45692</v>
+      </c>
+      <c r="E2390" t="s">
+        <v>150</v>
+      </c>
+      <c r="F2390" t="s">
+        <v>16</v>
+      </c>
+      <c r="G2390" t="s">
+        <v>54</v>
+      </c>
+      <c r="H2390" t="s">
+        <v>55</v>
+      </c>
+      <c r="I2390" t="s">
+        <v>26</v>
+      </c>
+      <c r="J2390" s="5">
+        <v>46246.623611111114</v>
+      </c>
+      <c r="K2390">
+        <v>8</v>
+      </c>
+      <c r="L2390">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2391" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2391">
+        <v>50187225</v>
+      </c>
+      <c r="B2391" s="5">
+        <v>46235</v>
+      </c>
+      <c r="C2391" t="s">
+        <v>144</v>
+      </c>
+      <c r="D2391" s="5">
+        <v>45929</v>
+      </c>
+      <c r="E2391" t="s">
+        <v>152</v>
+      </c>
+      <c r="F2391" t="s">
+        <v>11</v>
+      </c>
+      <c r="G2391" t="s">
+        <v>12</v>
+      </c>
+      <c r="H2391" t="s">
+        <v>13</v>
+      </c>
+      <c r="I2391" t="s">
+        <v>26</v>
+      </c>
+      <c r="J2391" s="5">
+        <v>46239.390277777777</v>
+      </c>
+      <c r="K2391">
+        <v>8</v>
+      </c>
+      <c r="L2391">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2392" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2392">
+        <v>50187957</v>
+      </c>
+      <c r="B2392" s="5">
+        <v>46241</v>
+      </c>
+      <c r="C2392" t="s">
+        <v>142</v>
+      </c>
+      <c r="D2392" s="5">
+        <v>45937</v>
+      </c>
+      <c r="E2392" t="s">
+        <v>152</v>
+      </c>
+      <c r="F2392" t="s">
+        <v>11</v>
+      </c>
+      <c r="G2392" t="s">
+        <v>12</v>
+      </c>
+      <c r="H2392" t="s">
+        <v>13</v>
+      </c>
+      <c r="I2392" t="s">
+        <v>26</v>
+      </c>
+      <c r="J2392" s="5">
+        <v>46252.365972222222</v>
+      </c>
+      <c r="K2392">
+        <v>8</v>
+      </c>
+      <c r="L2392">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2393" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2393">
+        <v>45270500</v>
+      </c>
+      <c r="B2393" s="5">
+        <v>46243</v>
+      </c>
+      <c r="C2393" t="s">
+        <v>142</v>
+      </c>
+      <c r="D2393" s="5">
+        <v>44144</v>
+      </c>
+      <c r="E2393" t="s">
+        <v>149</v>
+      </c>
+      <c r="F2393" t="s">
+        <v>31</v>
+      </c>
+      <c r="G2393" t="s">
+        <v>32</v>
+      </c>
+      <c r="H2393" t="s">
+        <v>37</v>
+      </c>
+      <c r="I2393" t="s">
+        <v>140</v>
+      </c>
+      <c r="J2393" s="5">
+        <v>46246.371527777781</v>
+      </c>
+      <c r="K2393">
+        <v>8</v>
+      </c>
+      <c r="L2393">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2394" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2394">
+        <v>23001647</v>
+      </c>
+      <c r="B2394" s="5">
+        <v>46235</v>
+      </c>
+      <c r="C2394" t="s">
+        <v>23</v>
+      </c>
+      <c r="D2394" s="5">
+        <v>45807</v>
+      </c>
+      <c r="E2394" t="s">
+        <v>150</v>
+      </c>
+      <c r="F2394" t="s">
+        <v>16</v>
+      </c>
+      <c r="G2394" t="s">
+        <v>17</v>
+      </c>
+      <c r="H2394" t="s">
+        <v>18</v>
+      </c>
+      <c r="I2394" t="s">
+        <v>140</v>
+      </c>
+      <c r="J2394" s="5">
+        <v>46239.364583333336</v>
+      </c>
+      <c r="K2394">
+        <v>8</v>
+      </c>
+      <c r="L2394">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2395" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2395">
+        <v>30103733</v>
+      </c>
+      <c r="B2395" s="5">
+        <v>46240</v>
+      </c>
+      <c r="C2395" t="s">
+        <v>142</v>
+      </c>
+      <c r="D2395" s="5">
+        <v>44018</v>
+      </c>
+      <c r="E2395" t="s">
+        <v>149</v>
+      </c>
+      <c r="F2395" t="s">
+        <v>11</v>
+      </c>
+      <c r="G2395" t="s">
+        <v>49</v>
+      </c>
+      <c r="H2395" t="s">
+        <v>52</v>
+      </c>
+      <c r="I2395" t="s">
+        <v>140</v>
+      </c>
+      <c r="J2395" s="5">
+        <v>46242.356249999997</v>
+      </c>
+      <c r="K2395">
+        <v>8</v>
+      </c>
+      <c r="L2395">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2396" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2396">
+        <v>30163094</v>
+      </c>
+      <c r="B2396" s="5">
+        <v>46238</v>
+      </c>
+      <c r="C2396" t="s">
+        <v>23</v>
+      </c>
+      <c r="D2396" s="5">
+        <v>45692</v>
+      </c>
+      <c r="E2396" t="s">
+        <v>150</v>
+      </c>
+      <c r="F2396" t="s">
+        <v>11</v>
+      </c>
+      <c r="G2396" t="s">
+        <v>49</v>
+      </c>
+      <c r="H2396" t="s">
+        <v>50</v>
+      </c>
+      <c r="I2396" t="s">
+        <v>140</v>
+      </c>
+      <c r="J2396" s="5">
+        <v>46241.724305555559</v>
+      </c>
+      <c r="K2396">
+        <v>8</v>
+      </c>
+      <c r="L2396">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2397" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2397">
+        <v>2104883</v>
+      </c>
+      <c r="B2397" s="5">
+        <v>46250</v>
+      </c>
+      <c r="C2397" t="s">
+        <v>142</v>
+      </c>
+      <c r="D2397" s="5">
+        <v>45185</v>
+      </c>
+      <c r="E2397" t="s">
+        <v>147</v>
+      </c>
+      <c r="F2397" t="s">
+        <v>11</v>
+      </c>
+      <c r="G2397" t="s">
+        <v>28</v>
+      </c>
+      <c r="H2397" t="s">
+        <v>34</v>
+      </c>
+      <c r="I2397" t="s">
+        <v>140</v>
+      </c>
+      <c r="J2397" s="5">
+        <v>46242.374305555553</v>
+      </c>
+      <c r="K2397">
+        <v>8</v>
+      </c>
+      <c r="L2397">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2398" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2398">
+        <v>20169658</v>
+      </c>
+      <c r="B2398" s="5">
+        <v>46238</v>
+      </c>
+      <c r="C2398" t="s">
+        <v>142</v>
+      </c>
+      <c r="D2398" s="5">
+        <v>45842</v>
+      </c>
+      <c r="E2398" t="s">
+        <v>150</v>
+      </c>
+      <c r="F2398" t="s">
+        <v>16</v>
+      </c>
+      <c r="G2398" t="s">
+        <v>20</v>
+      </c>
+      <c r="H2398" t="s">
+        <v>21</v>
+      </c>
+      <c r="I2398" t="s">
+        <v>140</v>
+      </c>
+      <c r="J2398" s="5">
+        <v>46241.734722222223</v>
+      </c>
+      <c r="K2398">
+        <v>8</v>
+      </c>
+      <c r="L2398">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2399" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2399">
+        <v>20181370</v>
+      </c>
+      <c r="B2399" s="5">
+        <v>46237</v>
+      </c>
+      <c r="C2399" t="s">
+        <v>23</v>
+      </c>
+      <c r="D2399" s="5">
+        <v>45933</v>
+      </c>
+      <c r="E2399" t="s">
+        <v>152</v>
+      </c>
+      <c r="F2399" t="s">
+        <v>16</v>
+      </c>
+      <c r="G2399" t="s">
+        <v>20</v>
+      </c>
+      <c r="H2399" t="s">
+        <v>57</v>
+      </c>
+      <c r="I2399" t="s">
+        <v>140</v>
+      </c>
+      <c r="J2399" s="5">
+        <v>46246.37777777778</v>
+      </c>
+      <c r="K2399">
+        <v>8</v>
+      </c>
+      <c r="L2399">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2400" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2400">
+        <v>20185186</v>
+      </c>
+      <c r="B2400" s="5">
+        <v>46235</v>
+      </c>
+      <c r="C2400" t="s">
+        <v>142</v>
+      </c>
+      <c r="D2400" s="5">
+        <v>45961</v>
+      </c>
+      <c r="E2400" t="s">
+        <v>152</v>
+      </c>
+      <c r="F2400" t="s">
+        <v>16</v>
+      </c>
+      <c r="G2400" t="s">
+        <v>20</v>
+      </c>
+      <c r="H2400" t="s">
+        <v>57</v>
+      </c>
+      <c r="I2400" t="s">
+        <v>140</v>
+      </c>
+      <c r="J2400" s="5">
+        <v>46247.617361111108</v>
+      </c>
+      <c r="K2400">
+        <v>8</v>
+      </c>
+      <c r="L2400">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2401" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2401">
+        <v>21107324</v>
+      </c>
+      <c r="B2401" s="5">
+        <v>46243</v>
+      </c>
+      <c r="C2401" t="s">
+        <v>142</v>
+      </c>
+      <c r="D2401" s="5">
+        <v>45300</v>
+      </c>
+      <c r="E2401" t="s">
+        <v>147</v>
+      </c>
+      <c r="F2401" t="s">
+        <v>16</v>
+      </c>
+      <c r="G2401" t="s">
+        <v>54</v>
+      </c>
+      <c r="H2401" t="s">
+        <v>55</v>
+      </c>
+      <c r="I2401" t="s">
+        <v>140</v>
+      </c>
+      <c r="J2401" s="5">
+        <v>46247.353472222225</v>
+      </c>
+      <c r="K2401">
+        <v>8</v>
+      </c>
+      <c r="L2401">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2402" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2402">
+        <v>31148632</v>
+      </c>
+      <c r="B2402" s="5">
+        <v>46243</v>
+      </c>
+      <c r="C2402" t="s">
+        <v>142</v>
+      </c>
+      <c r="D2402" s="5">
+        <v>45331</v>
+      </c>
+      <c r="E2402" t="s">
+        <v>147</v>
+      </c>
+      <c r="F2402" t="s">
+        <v>31</v>
+      </c>
+      <c r="G2402" t="s">
+        <v>45</v>
+      </c>
+      <c r="H2402" t="s">
+        <v>75</v>
+      </c>
+      <c r="I2402" t="s">
+        <v>140</v>
+      </c>
+      <c r="J2402" s="5">
+        <v>46248.355555555558</v>
+      </c>
+      <c r="K2402">
+        <v>8</v>
+      </c>
+      <c r="L2402">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2403" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2403">
+        <v>50128878</v>
+      </c>
+      <c r="B2403" s="5">
+        <v>46239</v>
+      </c>
+      <c r="C2403" t="s">
+        <v>142</v>
+      </c>
+      <c r="D2403" s="5">
+        <v>44747</v>
+      </c>
+      <c r="E2403" t="s">
+        <v>149</v>
+      </c>
+      <c r="F2403" t="s">
+        <v>11</v>
+      </c>
+      <c r="G2403" t="s">
+        <v>12</v>
+      </c>
+      <c r="H2403" t="s">
+        <v>13</v>
+      </c>
+      <c r="I2403" t="s">
+        <v>140</v>
+      </c>
+      <c r="J2403" s="5">
+        <v>46241.438888888886</v>
+      </c>
+      <c r="K2403">
+        <v>8</v>
+      </c>
+      <c r="L2403">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2404" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2404">
+        <v>35144328</v>
+      </c>
+      <c r="B2404" s="5">
+        <v>46251</v>
+      </c>
+      <c r="C2404" t="s">
+        <v>23</v>
+      </c>
+      <c r="D2404" s="5">
+        <v>43999</v>
+      </c>
+      <c r="E2404" t="s">
+        <v>149</v>
+      </c>
+      <c r="F2404" t="s">
+        <v>31</v>
+      </c>
+      <c r="G2404" t="s">
+        <v>40</v>
+      </c>
+      <c r="H2404" t="s">
+        <v>41</v>
+      </c>
+      <c r="I2404" t="s">
+        <v>162</v>
+      </c>
+      <c r="J2404" s="5">
+        <v>46244.695833333331</v>
+      </c>
+      <c r="K2404">
+        <v>8</v>
+      </c>
+      <c r="L2404">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2405" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2405">
+        <v>45397439</v>
+      </c>
+      <c r="B2405" s="5">
+        <v>46241</v>
+      </c>
+      <c r="C2405" t="s">
+        <v>62</v>
+      </c>
+      <c r="D2405" s="5">
+        <v>45695</v>
+      </c>
+      <c r="E2405" t="s">
+        <v>150</v>
+      </c>
+      <c r="F2405" t="s">
+        <v>31</v>
+      </c>
+      <c r="G2405" t="s">
+        <v>32</v>
+      </c>
+      <c r="H2405" t="s">
+        <v>93</v>
+      </c>
+      <c r="I2405" t="s">
+        <v>42</v>
+      </c>
+      <c r="J2405" s="5">
+        <v>46249.645833333336</v>
+      </c>
+      <c r="K2405">
+        <v>8</v>
+      </c>
+      <c r="L2405">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2406" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2406">
+        <v>45425635</v>
+      </c>
+      <c r="B2406" s="5">
+        <v>46241</v>
+      </c>
+      <c r="C2406" t="s">
+        <v>103</v>
+      </c>
+      <c r="D2406" s="5">
+        <v>46060</v>
+      </c>
+      <c r="E2406" t="s">
+        <v>151</v>
+      </c>
+      <c r="F2406" t="s">
+        <v>31</v>
+      </c>
+      <c r="G2406" t="s">
+        <v>32</v>
+      </c>
+      <c r="H2406" t="s">
+        <v>67</v>
+      </c>
+      <c r="I2406" t="s">
+        <v>42</v>
+      </c>
+      <c r="J2406" s="5">
+        <v>46249.64166666667</v>
+      </c>
+      <c r="K2406">
+        <v>8</v>
+      </c>
+      <c r="L2406">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2407" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2407">
+        <v>2192210</v>
+      </c>
+      <c r="B2407" s="5">
+        <v>46244</v>
+      </c>
+      <c r="C2407" t="s">
+        <v>157</v>
+      </c>
+      <c r="D2407" s="5">
+        <v>45971</v>
+      </c>
+      <c r="E2407" t="s">
+        <v>152</v>
+      </c>
+      <c r="F2407" t="s">
+        <v>11</v>
+      </c>
+      <c r="G2407" t="s">
+        <v>38</v>
+      </c>
+      <c r="H2407" t="s">
+        <v>29</v>
+      </c>
+      <c r="I2407" t="s">
+        <v>42</v>
+      </c>
+      <c r="J2407" s="5">
+        <v>46235.455555555556</v>
+      </c>
+      <c r="K2407">
+        <v>8</v>
+      </c>
+      <c r="L2407">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2408" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2408">
+        <v>21133480</v>
+      </c>
+      <c r="B2408" s="5">
+        <v>46243</v>
+      </c>
+      <c r="C2408" t="s">
+        <v>62</v>
+      </c>
+      <c r="D2408" s="5">
+        <v>45756</v>
+      </c>
+      <c r="E2408" t="s">
+        <v>150</v>
+      </c>
+      <c r="F2408" t="s">
+        <v>16</v>
+      </c>
+      <c r="G2408" t="s">
+        <v>54</v>
+      </c>
+      <c r="H2408" t="s">
+        <v>55</v>
+      </c>
+      <c r="I2408" t="s">
+        <v>42</v>
+      </c>
+      <c r="J2408" s="5">
+        <v>46247.349305555559</v>
+      </c>
+      <c r="K2408">
+        <v>8</v>
+      </c>
+      <c r="L2408">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2409" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2409">
+        <v>21141941</v>
+      </c>
+      <c r="B2409" s="5">
+        <v>46238</v>
+      </c>
+      <c r="C2409" t="s">
+        <v>62</v>
+      </c>
+      <c r="D2409" s="5">
+        <v>45842</v>
+      </c>
+      <c r="E2409" t="s">
+        <v>150</v>
+      </c>
+      <c r="F2409" t="s">
+        <v>16</v>
+      </c>
+      <c r="G2409" t="s">
+        <v>54</v>
+      </c>
+      <c r="H2409" t="s">
+        <v>55</v>
+      </c>
+      <c r="I2409" t="s">
+        <v>42</v>
+      </c>
+      <c r="J2409" s="5">
+        <v>46242.353472222225</v>
+      </c>
+      <c r="K2409">
+        <v>8</v>
+      </c>
+      <c r="L2409">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2410" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2410">
+        <v>21162688</v>
+      </c>
+      <c r="B2410" s="5">
+        <v>46243</v>
+      </c>
+      <c r="C2410" t="s">
+        <v>103</v>
+      </c>
+      <c r="D2410" s="5">
+        <v>46151</v>
+      </c>
+      <c r="E2410" t="s">
+        <v>153</v>
+      </c>
+      <c r="F2410" t="s">
+        <v>16</v>
+      </c>
+      <c r="G2410" t="s">
+        <v>54</v>
+      </c>
+      <c r="H2410" t="s">
+        <v>55</v>
+      </c>
+      <c r="I2410" t="s">
+        <v>42</v>
+      </c>
+      <c r="J2410" s="5">
+        <v>46247.354861111111</v>
+      </c>
+      <c r="K2410">
+        <v>8</v>
+      </c>
+      <c r="L2410">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2411" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2411">
+        <v>21164872</v>
+      </c>
+      <c r="B2411" s="5">
+        <v>46244</v>
+      </c>
+      <c r="C2411" t="s">
+        <v>103</v>
+      </c>
+      <c r="D2411" s="5">
+        <v>46183</v>
+      </c>
+      <c r="E2411" t="s">
+        <v>148</v>
+      </c>
+      <c r="F2411" t="s">
+        <v>16</v>
+      </c>
+      <c r="G2411" t="s">
+        <v>54</v>
+      </c>
+      <c r="H2411" t="s">
+        <v>55</v>
+      </c>
+      <c r="I2411" t="s">
+        <v>42</v>
+      </c>
+      <c r="J2411" s="5">
+        <v>46249.35833333333</v>
+      </c>
+      <c r="K2411">
+        <v>8</v>
+      </c>
+      <c r="L2411">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2412" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2412">
+        <v>31158708</v>
+      </c>
+      <c r="B2412" s="5">
+        <v>46238</v>
+      </c>
+      <c r="C2412" t="s">
+        <v>62</v>
+      </c>
+      <c r="D2412" s="5">
+        <v>45630</v>
+      </c>
+      <c r="E2412" t="s">
+        <v>150</v>
+      </c>
+      <c r="F2412" t="s">
+        <v>31</v>
+      </c>
+      <c r="G2412" t="s">
+        <v>45</v>
+      </c>
+      <c r="H2412" t="s">
+        <v>46</v>
+      </c>
+      <c r="I2412" t="s">
+        <v>42</v>
+      </c>
+      <c r="J2412" s="5">
+        <v>46242.356944444444</v>
+      </c>
+      <c r="K2412">
+        <v>8</v>
+      </c>
+      <c r="L2412">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2413" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2413">
+        <v>31159451</v>
+      </c>
+      <c r="B2413" s="5">
+        <v>46244</v>
+      </c>
+      <c r="C2413" t="s">
+        <v>62</v>
+      </c>
+      <c r="D2413" s="5">
+        <v>45636</v>
+      </c>
+      <c r="E2413" t="s">
+        <v>150</v>
+      </c>
+      <c r="F2413" t="s">
+        <v>31</v>
+      </c>
+      <c r="G2413" t="s">
+        <v>45</v>
+      </c>
+      <c r="H2413" t="s">
+        <v>75</v>
+      </c>
+      <c r="I2413" t="s">
+        <v>42</v>
+      </c>
+      <c r="J2413" s="5">
+        <v>46252.368055555555</v>
+      </c>
+      <c r="K2413">
+        <v>8</v>
+      </c>
+      <c r="L2413">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2414" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2414">
+        <v>31184799</v>
+      </c>
+      <c r="B2414" s="5">
+        <v>46241</v>
+      </c>
+      <c r="C2414" t="s">
+        <v>62</v>
+      </c>
+      <c r="D2414" s="5">
+        <v>45968</v>
+      </c>
+      <c r="E2414" t="s">
+        <v>152</v>
+      </c>
+      <c r="F2414" t="s">
+        <v>31</v>
+      </c>
+      <c r="G2414" t="s">
+        <v>45</v>
+      </c>
+      <c r="H2414" t="s">
+        <v>75</v>
+      </c>
+      <c r="I2414" t="s">
+        <v>42</v>
+      </c>
+      <c r="J2414" s="5">
+        <v>46244.376388888886</v>
+      </c>
+      <c r="K2414">
+        <v>8</v>
+      </c>
+      <c r="L2414">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2415" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2415">
+        <v>45423693</v>
+      </c>
+      <c r="B2415" s="5">
+        <v>46243</v>
+      </c>
+      <c r="C2415" t="s">
+        <v>62</v>
+      </c>
+      <c r="D2415" s="5">
+        <v>46031</v>
+      </c>
+      <c r="E2415" t="s">
+        <v>151</v>
+      </c>
+      <c r="F2415" t="s">
+        <v>31</v>
+      </c>
+      <c r="G2415" t="s">
+        <v>32</v>
+      </c>
+      <c r="H2415" t="s">
+        <v>93</v>
+      </c>
+      <c r="I2415" t="s">
+        <v>27</v>
+      </c>
+      <c r="J2415" s="5">
+        <v>46249.660416666666</v>
+      </c>
+      <c r="K2415">
+        <v>8</v>
+      </c>
+      <c r="L2415">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2416" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2416">
+        <v>45427549</v>
+      </c>
+      <c r="B2416" s="5">
+        <v>46236</v>
+      </c>
+      <c r="C2416" t="s">
+        <v>103</v>
+      </c>
+      <c r="D2416" s="5">
+        <v>46083</v>
+      </c>
+      <c r="E2416" t="s">
+        <v>153</v>
+      </c>
+      <c r="F2416" t="s">
+        <v>31</v>
+      </c>
+      <c r="G2416" t="s">
+        <v>32</v>
+      </c>
+      <c r="H2416" t="s">
+        <v>93</v>
+      </c>
+      <c r="I2416" t="s">
+        <v>27</v>
+      </c>
+      <c r="J2416" s="5">
+        <v>46240.281944444447</v>
+      </c>
+      <c r="K2416">
+        <v>8</v>
+      </c>
+      <c r="L2416">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2417" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2417">
+        <v>45434697</v>
+      </c>
+      <c r="B2417" s="5">
+        <v>46242</v>
+      </c>
+      <c r="C2417" t="s">
+        <v>103</v>
+      </c>
+      <c r="D2417" s="5">
+        <v>46181</v>
+      </c>
+      <c r="E2417" t="s">
+        <v>148</v>
+      </c>
+      <c r="F2417" t="s">
+        <v>31</v>
+      </c>
+      <c r="G2417" t="s">
+        <v>32</v>
+      </c>
+      <c r="H2417" t="s">
+        <v>128</v>
+      </c>
+      <c r="I2417" t="s">
+        <v>27</v>
+      </c>
+      <c r="J2417" s="5">
+        <v>46246.283333333333</v>
+      </c>
+      <c r="K2417">
+        <v>8</v>
+      </c>
+      <c r="L2417">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2418" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2418">
+        <v>35224704</v>
+      </c>
+      <c r="B2418" s="5">
+        <v>46243</v>
+      </c>
+      <c r="C2418" t="s">
+        <v>156</v>
+      </c>
+      <c r="D2418" s="5">
+        <v>45817</v>
+      </c>
+      <c r="E2418" t="s">
+        <v>150</v>
+      </c>
+      <c r="F2418" t="s">
+        <v>31</v>
+      </c>
+      <c r="G2418" t="s">
+        <v>40</v>
+      </c>
+      <c r="H2418" t="s">
+        <v>72</v>
+      </c>
+      <c r="I2418" t="s">
+        <v>27</v>
+      </c>
+      <c r="J2418" s="5">
+        <v>46248.71875</v>
+      </c>
+      <c r="K2418">
+        <v>8</v>
+      </c>
+      <c r="L2418">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2419" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2419">
+        <v>30188621</v>
+      </c>
+      <c r="B2419" s="5">
+        <v>46243</v>
+      </c>
+      <c r="C2419" t="s">
+        <v>103</v>
+      </c>
+      <c r="D2419" s="5">
+        <v>46090</v>
+      </c>
+      <c r="E2419" t="s">
+        <v>153</v>
+      </c>
+      <c r="F2419" t="s">
+        <v>11</v>
+      </c>
+      <c r="G2419" t="s">
+        <v>49</v>
+      </c>
+      <c r="H2419" t="s">
+        <v>50</v>
+      </c>
+      <c r="I2419" t="s">
+        <v>27</v>
+      </c>
+      <c r="J2419" s="5">
+        <v>46248.714583333334</v>
+      </c>
+      <c r="K2419">
+        <v>8</v>
+      </c>
+      <c r="L2419">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2420" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2420">
+        <v>20155225</v>
+      </c>
+      <c r="B2420" s="5">
+        <v>46247</v>
+      </c>
+      <c r="C2420" t="s">
+        <v>142</v>
+      </c>
+      <c r="D2420" s="5">
+        <v>45729</v>
+      </c>
+      <c r="E2420" t="s">
+        <v>150</v>
+      </c>
+      <c r="F2420" t="s">
+        <v>16</v>
+      </c>
+      <c r="G2420" t="s">
+        <v>20</v>
+      </c>
+      <c r="H2420" t="s">
+        <v>21</v>
+      </c>
+      <c r="I2420" t="s">
+        <v>27</v>
+      </c>
+      <c r="J2420" s="5">
+        <v>46252.311805555553</v>
+      </c>
+      <c r="K2420">
+        <v>8</v>
+      </c>
+      <c r="L2420">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2421" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2421">
+        <v>21162630</v>
+      </c>
+      <c r="B2421" s="5">
+        <v>46242</v>
+      </c>
+      <c r="C2421" t="s">
+        <v>103</v>
+      </c>
+      <c r="D2421" s="5">
+        <v>46150</v>
+      </c>
+      <c r="E2421" t="s">
+        <v>153</v>
+      </c>
+      <c r="F2421" t="s">
+        <v>16</v>
+      </c>
+      <c r="G2421" t="s">
+        <v>54</v>
+      </c>
+      <c r="H2421" t="s">
+        <v>55</v>
+      </c>
+      <c r="I2421" t="s">
+        <v>27</v>
+      </c>
+      <c r="J2421" s="5">
+        <v>46249.654166666667</v>
+      </c>
+      <c r="K2421">
+        <v>8</v>
+      </c>
+      <c r="L2421">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2422" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2422">
+        <v>33032460</v>
+      </c>
+      <c r="B2422" s="5">
+        <v>46237</v>
+      </c>
+      <c r="C2422" t="s">
+        <v>103</v>
+      </c>
+      <c r="D2422" s="5">
+        <v>46056</v>
+      </c>
+      <c r="E2422" t="s">
+        <v>151</v>
+      </c>
+      <c r="F2422" t="s">
+        <v>31</v>
+      </c>
+      <c r="G2422" t="s">
+        <v>43</v>
+      </c>
+      <c r="H2422" t="s">
+        <v>161</v>
+      </c>
+      <c r="I2422" t="s">
+        <v>27</v>
+      </c>
+      <c r="J2422" s="5">
+        <v>46240.284722222219</v>
+      </c>
+      <c r="K2422">
+        <v>8</v>
+      </c>
+      <c r="L2422">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2423" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2423">
+        <v>45293837</v>
+      </c>
+      <c r="B2423" s="5">
+        <v>46240</v>
+      </c>
+      <c r="C2423" t="s">
+        <v>23</v>
+      </c>
+      <c r="D2423" s="5">
+        <v>44475</v>
+      </c>
+      <c r="E2423" t="s">
+        <v>149</v>
+      </c>
+      <c r="F2423" t="s">
+        <v>31</v>
+      </c>
+      <c r="G2423" t="s">
+        <v>32</v>
+      </c>
+      <c r="H2423" t="s">
+        <v>33</v>
+      </c>
+      <c r="I2423" t="s">
+        <v>39</v>
+      </c>
+      <c r="J2423" s="5">
+        <v>46245.31527777778</v>
+      </c>
+      <c r="K2423">
+        <v>8</v>
+      </c>
+      <c r="L2423">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2424" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2424">
+        <v>41008996</v>
+      </c>
+      <c r="B2424" s="5">
+        <v>46240</v>
+      </c>
+      <c r="C2424" t="s">
+        <v>62</v>
+      </c>
+      <c r="D2424" s="5">
+        <v>46059</v>
+      </c>
+      <c r="E2424" t="s">
+        <v>151</v>
+      </c>
+      <c r="F2424" t="s">
+        <v>31</v>
+      </c>
+      <c r="G2424" t="s">
+        <v>69</v>
+      </c>
+      <c r="H2424" t="s">
+        <v>134</v>
+      </c>
+      <c r="I2424" t="s">
+        <v>39</v>
+      </c>
+      <c r="J2424" s="5">
+        <v>46251.663194444445</v>
+      </c>
+      <c r="K2424">
+        <v>8</v>
+      </c>
+      <c r="L2424">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2425" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2425">
+        <v>2153194</v>
+      </c>
+      <c r="B2425" s="5">
+        <v>46238</v>
+      </c>
+      <c r="C2425" t="s">
+        <v>62</v>
+      </c>
+      <c r="D2425" s="5">
+        <v>45692</v>
+      </c>
+      <c r="E2425" t="s">
+        <v>150</v>
+      </c>
+      <c r="F2425" t="s">
+        <v>11</v>
+      </c>
+      <c r="G2425" t="s">
+        <v>38</v>
+      </c>
+      <c r="H2425" t="s">
+        <v>60</v>
+      </c>
+      <c r="I2425" t="s">
+        <v>39</v>
+      </c>
+      <c r="J2425" s="5">
+        <v>46242.771527777775</v>
+      </c>
+      <c r="K2425">
+        <v>8</v>
+      </c>
+      <c r="L2425">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2426" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2426">
+        <v>60010352</v>
+      </c>
+      <c r="B2426" s="5">
+        <v>46242</v>
+      </c>
+      <c r="C2426" t="s">
+        <v>62</v>
+      </c>
+      <c r="D2426" s="5">
+        <v>45877</v>
+      </c>
+      <c r="E2426" t="s">
+        <v>150</v>
+      </c>
+      <c r="F2426" t="s">
+        <v>31</v>
+      </c>
+      <c r="G2426" t="s">
+        <v>63</v>
+      </c>
+      <c r="H2426" t="s">
+        <v>64</v>
+      </c>
+      <c r="I2426" t="s">
+        <v>39</v>
+      </c>
+      <c r="J2426" s="5">
+        <v>46245.352083333331</v>
+      </c>
+      <c r="K2426">
+        <v>8</v>
+      </c>
+      <c r="L2426">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2427" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2427">
+        <v>60014662</v>
+      </c>
+      <c r="B2427" s="5">
+        <v>46244</v>
+      </c>
+      <c r="C2427" t="s">
+        <v>62</v>
+      </c>
+      <c r="D2427" s="5">
+        <v>46032</v>
+      </c>
+      <c r="E2427" t="s">
+        <v>151</v>
+      </c>
+      <c r="F2427" t="s">
+        <v>31</v>
+      </c>
+      <c r="G2427" t="s">
+        <v>63</v>
+      </c>
+      <c r="H2427" t="s">
+        <v>64</v>
+      </c>
+      <c r="I2427" t="s">
+        <v>39</v>
+      </c>
+      <c r="J2427" s="5">
+        <v>46251.640277777777</v>
+      </c>
+      <c r="K2427">
+        <v>8</v>
+      </c>
+      <c r="L2427">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2428" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2428">
+        <v>22001696</v>
+      </c>
+      <c r="B2428" s="5">
+        <v>46245</v>
+      </c>
+      <c r="C2428" t="s">
+        <v>142</v>
+      </c>
+      <c r="D2428" s="5">
+        <v>45819</v>
+      </c>
+      <c r="E2428" t="s">
+        <v>150</v>
+      </c>
+      <c r="F2428" t="s">
+        <v>16</v>
+      </c>
+      <c r="G2428" t="s">
+        <v>100</v>
+      </c>
+      <c r="H2428" t="s">
+        <v>111</v>
+      </c>
+      <c r="I2428" t="s">
+        <v>39</v>
+      </c>
+      <c r="J2428" s="5">
+        <v>46251.668055555558</v>
+      </c>
+      <c r="K2428">
+        <v>8</v>
+      </c>
+      <c r="L2428">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2429" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2429">
+        <v>21158862</v>
+      </c>
+      <c r="B2429" s="5">
+        <v>46245</v>
+      </c>
+      <c r="C2429" t="s">
+        <v>103</v>
+      </c>
+      <c r="D2429" s="5">
+        <v>46092</v>
+      </c>
+      <c r="E2429" t="s">
+        <v>153</v>
+      </c>
+      <c r="F2429" t="s">
+        <v>16</v>
+      </c>
+      <c r="G2429" t="s">
+        <v>54</v>
+      </c>
+      <c r="H2429" t="s">
+        <v>55</v>
+      </c>
+      <c r="I2429" t="s">
+        <v>39</v>
+      </c>
+      <c r="J2429" s="5">
+        <v>46251.32708333333</v>
+      </c>
+      <c r="K2429">
+        <v>8</v>
+      </c>
+      <c r="L2429">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2430" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2430">
+        <v>21160294</v>
+      </c>
+      <c r="B2430" s="5">
+        <v>46240</v>
+      </c>
+      <c r="C2430" t="s">
+        <v>103</v>
+      </c>
+      <c r="D2430" s="5">
+        <v>46118</v>
+      </c>
+      <c r="E2430" t="s">
+        <v>153</v>
+      </c>
+      <c r="F2430" t="s">
+        <v>16</v>
+      </c>
+      <c r="G2430" t="s">
+        <v>54</v>
+      </c>
+      <c r="H2430" t="s">
+        <v>55</v>
+      </c>
+      <c r="I2430" t="s">
+        <v>39</v>
+      </c>
+      <c r="J2430" s="5">
+        <v>46242.78402777778</v>
+      </c>
+      <c r="K2430">
+        <v>8</v>
+      </c>
+      <c r="L2430">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2431" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2431">
+        <v>31167563</v>
+      </c>
+      <c r="B2431" s="5">
+        <v>46245</v>
+      </c>
+      <c r="C2431" t="s">
+        <v>23</v>
+      </c>
+      <c r="D2431" s="5">
+        <v>45758</v>
+      </c>
+      <c r="E2431" t="s">
+        <v>150</v>
+      </c>
+      <c r="F2431" t="s">
+        <v>31</v>
+      </c>
+      <c r="G2431" t="s">
+        <v>45</v>
+      </c>
+      <c r="H2431" t="s">
+        <v>75</v>
+      </c>
+      <c r="I2431" t="s">
+        <v>39</v>
+      </c>
+      <c r="J2431" s="5">
+        <v>46251.646527777775</v>
+      </c>
+      <c r="K2431">
+        <v>8</v>
+      </c>
+      <c r="L2431">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2432" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2432">
+        <v>45408593</v>
+      </c>
+      <c r="B2432" s="5">
+        <v>46241</v>
+      </c>
+      <c r="C2432" t="s">
+        <v>23</v>
+      </c>
+      <c r="D2432" s="5">
+        <v>45815</v>
+      </c>
+      <c r="E2432" t="s">
+        <v>150</v>
+      </c>
+      <c r="F2432" t="s">
+        <v>31</v>
+      </c>
+      <c r="G2432" t="s">
+        <v>32</v>
+      </c>
+      <c r="H2432" t="s">
+        <v>33</v>
+      </c>
+      <c r="I2432" t="s">
+        <v>14</v>
+      </c>
+      <c r="J2432" s="5">
+        <v>46246.365972222222</v>
+      </c>
+      <c r="K2432">
+        <v>8</v>
+      </c>
+      <c r="L2432">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2433" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2433">
+        <v>35177587</v>
+      </c>
+      <c r="B2433" s="5">
+        <v>46244</v>
+      </c>
+      <c r="C2433" t="s">
+        <v>23</v>
+      </c>
+      <c r="D2433" s="5">
+        <v>44722</v>
+      </c>
+      <c r="E2433" t="s">
+        <v>149</v>
+      </c>
+      <c r="F2433" t="s">
+        <v>31</v>
+      </c>
+      <c r="G2433" t="s">
+        <v>40</v>
+      </c>
+      <c r="H2433" t="s">
+        <v>41</v>
+      </c>
+      <c r="I2433" t="s">
+        <v>14</v>
+      </c>
+      <c r="J2433" s="5">
+        <v>46251.337500000001</v>
+      </c>
+      <c r="K2433">
+        <v>8</v>
+      </c>
+      <c r="L2433">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2434" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2434">
+        <v>35184499</v>
+      </c>
+      <c r="B2434" s="5">
+        <v>46247</v>
+      </c>
+      <c r="C2434" t="s">
+        <v>62</v>
+      </c>
+      <c r="D2434" s="5">
+        <v>44908</v>
+      </c>
+      <c r="E2434" t="s">
+        <v>149</v>
+      </c>
+      <c r="F2434" t="s">
+        <v>31</v>
+      </c>
+      <c r="G2434" t="s">
+        <v>40</v>
+      </c>
+      <c r="H2434" t="s">
+        <v>41</v>
+      </c>
+      <c r="I2434" t="s">
+        <v>14</v>
+      </c>
+      <c r="J2434" s="5">
+        <v>46251.482638888891</v>
+      </c>
+      <c r="K2434">
+        <v>8</v>
+      </c>
+      <c r="L2434">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2435" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2435">
+        <v>35220044</v>
+      </c>
+      <c r="B2435" s="5">
+        <v>46243</v>
+      </c>
+      <c r="C2435" t="s">
+        <v>23</v>
+      </c>
+      <c r="D2435" s="5">
+        <v>45756</v>
+      </c>
+      <c r="E2435" t="s">
+        <v>150</v>
+      </c>
+      <c r="F2435" t="s">
+        <v>31</v>
+      </c>
+      <c r="G2435" t="s">
+        <v>40</v>
+      </c>
+      <c r="H2435" t="s">
+        <v>94</v>
+      </c>
+      <c r="I2435" t="s">
+        <v>14</v>
+      </c>
+      <c r="J2435" s="5">
+        <v>46246.36041666667</v>
+      </c>
+      <c r="K2435">
+        <v>8</v>
+      </c>
+      <c r="L2435">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2436" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2436">
+        <v>35244579</v>
+      </c>
+      <c r="B2436" s="5">
+        <v>46243</v>
+      </c>
+      <c r="C2436" t="s">
+        <v>103</v>
+      </c>
+      <c r="D2436" s="5">
+        <v>46090</v>
+      </c>
+      <c r="E2436" t="s">
+        <v>153</v>
+      </c>
+      <c r="F2436" t="s">
+        <v>31</v>
+      </c>
+      <c r="G2436" t="s">
+        <v>40</v>
+      </c>
+      <c r="H2436" t="s">
+        <v>159</v>
+      </c>
+      <c r="I2436" t="s">
+        <v>14</v>
+      </c>
+      <c r="J2436" s="5">
+        <v>46245.345833333333</v>
+      </c>
+      <c r="K2436">
+        <v>8</v>
+      </c>
+      <c r="L2436">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2437" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2437">
+        <v>2149516</v>
+      </c>
+      <c r="B2437" s="5">
+        <v>46242</v>
+      </c>
+      <c r="C2437" t="s">
+        <v>142</v>
+      </c>
+      <c r="D2437" s="5">
+        <v>45665</v>
+      </c>
+      <c r="E2437" t="s">
+        <v>150</v>
+      </c>
+      <c r="F2437" t="s">
+        <v>11</v>
+      </c>
+      <c r="G2437" t="s">
+        <v>28</v>
+      </c>
+      <c r="H2437" t="s">
+        <v>48</v>
+      </c>
+      <c r="I2437" t="s">
+        <v>14</v>
+      </c>
+      <c r="J2437" s="5">
+        <v>46251.331944444442</v>
+      </c>
+      <c r="K2437">
+        <v>8</v>
+      </c>
+      <c r="L2437">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2438" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2438">
+        <v>2188339</v>
+      </c>
+      <c r="B2438" s="5">
+        <v>46242</v>
+      </c>
+      <c r="C2438" t="s">
+        <v>62</v>
+      </c>
+      <c r="D2438" s="5">
+        <v>45938</v>
+      </c>
+      <c r="E2438" t="s">
+        <v>152</v>
+      </c>
+      <c r="F2438" t="s">
+        <v>11</v>
+      </c>
+      <c r="G2438" t="s">
+        <v>38</v>
+      </c>
+      <c r="H2438" t="s">
+        <v>77</v>
+      </c>
+      <c r="I2438" t="s">
+        <v>14</v>
+      </c>
+      <c r="J2438" s="5">
+        <v>46251.319444444445</v>
+      </c>
+      <c r="K2438">
+        <v>8</v>
+      </c>
+      <c r="L2438">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2439" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2439">
+        <v>20150949</v>
+      </c>
+      <c r="B2439" s="5">
+        <v>46242</v>
+      </c>
+      <c r="C2439" t="s">
+        <v>142</v>
+      </c>
+      <c r="D2439" s="5">
+        <v>45696</v>
+      </c>
+      <c r="E2439" t="s">
+        <v>150</v>
+      </c>
+      <c r="F2439" t="s">
+        <v>16</v>
+      </c>
+      <c r="G2439" t="s">
+        <v>20</v>
+      </c>
+      <c r="H2439" t="s">
+        <v>57</v>
+      </c>
+      <c r="I2439" t="s">
+        <v>14</v>
+      </c>
+      <c r="J2439" s="5">
+        <v>46247.343055555553</v>
+      </c>
+      <c r="K2439">
+        <v>8</v>
+      </c>
+      <c r="L2439">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2440" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2440">
+        <v>20178044</v>
+      </c>
+      <c r="B2440" s="5">
+        <v>46243</v>
+      </c>
+      <c r="C2440" t="s">
+        <v>144</v>
+      </c>
+      <c r="D2440" s="5">
+        <v>45909</v>
+      </c>
+      <c r="E2440" t="s">
+        <v>152</v>
+      </c>
+      <c r="F2440" t="s">
+        <v>16</v>
+      </c>
+      <c r="G2440" t="s">
+        <v>20</v>
+      </c>
+      <c r="H2440" t="s">
+        <v>79</v>
+      </c>
+      <c r="I2440" t="s">
+        <v>14</v>
+      </c>
+      <c r="J2440" s="5">
+        <v>46251.640277777777</v>
+      </c>
+      <c r="K2440">
+        <v>8</v>
+      </c>
+      <c r="L2440">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2441" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2441">
+        <v>20211845</v>
+      </c>
+      <c r="B2441" s="5">
+        <v>46242</v>
+      </c>
+      <c r="C2441" t="s">
+        <v>103</v>
+      </c>
+      <c r="D2441" s="5">
+        <v>46150</v>
+      </c>
+      <c r="E2441" t="s">
+        <v>153</v>
+      </c>
+      <c r="F2441" t="s">
+        <v>16</v>
+      </c>
+      <c r="G2441" t="s">
+        <v>20</v>
+      </c>
+      <c r="H2441" t="s">
+        <v>21</v>
+      </c>
+      <c r="I2441" t="s">
+        <v>14</v>
+      </c>
+      <c r="J2441" s="5">
+        <v>46248.622916666667</v>
+      </c>
+      <c r="K2441">
+        <v>8</v>
+      </c>
+      <c r="L2441">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2442" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2442">
+        <v>22001671</v>
+      </c>
+      <c r="B2442" s="5">
+        <v>46238</v>
+      </c>
+      <c r="C2442" t="s">
+        <v>62</v>
+      </c>
+      <c r="D2442" s="5">
+        <v>45934</v>
+      </c>
+      <c r="E2442" t="s">
+        <v>152</v>
+      </c>
+      <c r="F2442" t="s">
+        <v>16</v>
+      </c>
+      <c r="G2442" t="s">
+        <v>100</v>
+      </c>
+      <c r="H2442" t="s">
+        <v>111</v>
+      </c>
+      <c r="I2442" t="s">
+        <v>14</v>
+      </c>
+      <c r="J2442" s="5">
+        <v>46242.363194444442</v>
+      </c>
+      <c r="K2442">
+        <v>8</v>
+      </c>
+      <c r="L2442">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2443" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2443">
+        <v>21133394</v>
+      </c>
+      <c r="B2443" s="5">
+        <v>46243</v>
+      </c>
+      <c r="C2443" t="s">
+        <v>23</v>
+      </c>
+      <c r="D2443" s="5">
+        <v>45756</v>
+      </c>
+      <c r="E2443" t="s">
+        <v>150</v>
+      </c>
+      <c r="F2443" t="s">
+        <v>16</v>
+      </c>
+      <c r="G2443" t="s">
+        <v>54</v>
+      </c>
+      <c r="H2443" t="s">
+        <v>55</v>
+      </c>
+      <c r="I2443" t="s">
+        <v>14</v>
+      </c>
+      <c r="J2443" s="5">
+        <v>46248.370833333334</v>
+      </c>
+      <c r="K2443">
+        <v>8</v>
+      </c>
+      <c r="L2443">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2444" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2444">
+        <v>31180220</v>
+      </c>
+      <c r="B2444" s="5">
+        <v>46243</v>
+      </c>
+      <c r="C2444" t="s">
+        <v>62</v>
+      </c>
+      <c r="D2444" s="5">
+        <v>45909</v>
+      </c>
+      <c r="E2444" t="s">
+        <v>152</v>
+      </c>
+      <c r="F2444" t="s">
+        <v>31</v>
+      </c>
+      <c r="G2444" t="s">
+        <v>45</v>
+      </c>
+      <c r="H2444" t="s">
+        <v>46</v>
+      </c>
+      <c r="I2444" t="s">
+        <v>14</v>
+      </c>
+      <c r="J2444" s="5">
+        <v>46251.642361111109</v>
+      </c>
+      <c r="K2444">
+        <v>8</v>
+      </c>
+      <c r="L2444">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2445" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2445">
+        <v>31192628</v>
+      </c>
+      <c r="B2445" s="5">
+        <v>46243</v>
+      </c>
+      <c r="C2445" t="s">
+        <v>103</v>
+      </c>
+      <c r="D2445" s="5">
+        <v>46062</v>
+      </c>
+      <c r="E2445" t="s">
+        <v>151</v>
+      </c>
+      <c r="F2445" t="s">
+        <v>31</v>
+      </c>
+      <c r="G2445" t="s">
+        <v>45</v>
+      </c>
+      <c r="H2445" t="s">
+        <v>75</v>
+      </c>
+      <c r="I2445" t="s">
+        <v>14</v>
+      </c>
+      <c r="J2445" s="5">
+        <v>46246.368055555555</v>
+      </c>
+      <c r="K2445">
+        <v>8</v>
+      </c>
+      <c r="L2445">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2446" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2446">
+        <v>50108514</v>
+      </c>
+      <c r="B2446" s="5">
+        <v>46243</v>
+      </c>
+      <c r="C2446" t="s">
+        <v>23</v>
+      </c>
+      <c r="D2446" s="5">
+        <v>44264</v>
+      </c>
+      <c r="E2446" t="s">
+        <v>149</v>
+      </c>
+      <c r="F2446" t="s">
+        <v>11</v>
+      </c>
+      <c r="G2446" t="s">
+        <v>12</v>
+      </c>
+      <c r="H2446" t="s">
+        <v>24</v>
+      </c>
+      <c r="I2446" t="s">
+        <v>14</v>
+      </c>
+      <c r="J2446" s="5">
+        <v>46237.466666666667</v>
+      </c>
+      <c r="K2446">
+        <v>8</v>
+      </c>
+      <c r="L2446">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2447" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2447">
+        <v>50185055</v>
+      </c>
+      <c r="B2447" s="5">
+        <v>46235</v>
+      </c>
+      <c r="C2447" t="s">
+        <v>62</v>
+      </c>
+      <c r="D2447" s="5">
+        <v>45898</v>
+      </c>
+      <c r="E2447" t="s">
+        <v>152</v>
+      </c>
+      <c r="F2447" t="s">
+        <v>11</v>
+      </c>
+      <c r="G2447" t="s">
+        <v>12</v>
+      </c>
+      <c r="H2447" t="s">
+        <v>13</v>
+      </c>
+      <c r="I2447" t="s">
+        <v>14</v>
+      </c>
+      <c r="J2447" s="5">
+        <v>46239.426388888889</v>
+      </c>
+      <c r="K2447">
+        <v>8</v>
+      </c>
+      <c r="L2447">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2448" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2448">
+        <v>45317748</v>
+      </c>
+      <c r="B2448" s="5">
+        <v>46243</v>
+      </c>
+      <c r="C2448" t="s">
+        <v>154</v>
+      </c>
+      <c r="D2448" s="5">
+        <v>45116</v>
+      </c>
+      <c r="E2448" t="s">
+        <v>149</v>
+      </c>
+      <c r="F2448" t="s">
+        <v>31</v>
+      </c>
+      <c r="G2448" t="s">
+        <v>32</v>
+      </c>
+      <c r="H2448" t="s">
+        <v>37</v>
+      </c>
+      <c r="I2448" t="s">
+        <v>51</v>
+      </c>
+      <c r="J2448" s="5">
+        <v>46246.48541666667</v>
+      </c>
+      <c r="K2448">
+        <v>8</v>
+      </c>
+      <c r="L2448">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2449" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2449">
+        <v>45420806</v>
+      </c>
+      <c r="B2449" s="5">
+        <v>46235</v>
+      </c>
+      <c r="C2449" t="s">
+        <v>62</v>
+      </c>
+      <c r="D2449" s="5">
+        <v>45990</v>
+      </c>
+      <c r="E2449" t="s">
+        <v>151</v>
+      </c>
+      <c r="F2449" t="s">
+        <v>31</v>
+      </c>
+      <c r="G2449" t="s">
+        <v>32</v>
+      </c>
+      <c r="H2449" t="s">
+        <v>93</v>
+      </c>
+      <c r="I2449" t="s">
+        <v>51</v>
+      </c>
+      <c r="J2449" s="5">
+        <v>46239.367361111108</v>
+      </c>
+      <c r="K2449">
+        <v>8</v>
+      </c>
+      <c r="L2449">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2450" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2450">
+        <v>45426176</v>
+      </c>
+      <c r="B2450" s="5">
+        <v>46246</v>
+      </c>
+      <c r="C2450" t="s">
+        <v>103</v>
+      </c>
+      <c r="D2450" s="5">
+        <v>46065</v>
+      </c>
+      <c r="E2450" t="s">
+        <v>151</v>
+      </c>
+      <c r="F2450" t="s">
+        <v>31</v>
+      </c>
+      <c r="G2450" t="s">
+        <v>32</v>
+      </c>
+      <c r="H2450" t="s">
+        <v>68</v>
+      </c>
+      <c r="I2450" t="s">
+        <v>51</v>
+      </c>
+      <c r="J2450" s="5">
+        <v>46252.34375</v>
+      </c>
+      <c r="K2450">
+        <v>8</v>
+      </c>
+      <c r="L2450">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2451" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2451">
+        <v>45428030</v>
+      </c>
+      <c r="B2451" s="5">
+        <v>46242</v>
+      </c>
+      <c r="C2451" t="s">
+        <v>103</v>
+      </c>
+      <c r="D2451" s="5">
+        <v>46089</v>
+      </c>
+      <c r="E2451" t="s">
+        <v>153</v>
+      </c>
+      <c r="F2451" t="s">
+        <v>31</v>
+      </c>
+      <c r="G2451" t="s">
+        <v>32</v>
+      </c>
+      <c r="H2451" t="s">
+        <v>33</v>
+      </c>
+      <c r="I2451" t="s">
+        <v>51</v>
+      </c>
+      <c r="J2451" s="5">
+        <v>46251.373611111114</v>
+      </c>
+      <c r="K2451">
+        <v>8</v>
+      </c>
+      <c r="L2451">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2452" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2452">
+        <v>35082064</v>
+      </c>
+      <c r="B2452" s="5">
+        <v>46235</v>
+      </c>
+      <c r="C2452" t="s">
+        <v>142</v>
+      </c>
+      <c r="D2452" s="5">
+        <v>44440</v>
+      </c>
+      <c r="E2452" t="s">
+        <v>149</v>
+      </c>
+      <c r="F2452" t="s">
+        <v>31</v>
+      </c>
+      <c r="G2452" t="s">
+        <v>40</v>
+      </c>
+      <c r="H2452" t="s">
+        <v>41</v>
+      </c>
+      <c r="I2452" t="s">
+        <v>51</v>
+      </c>
+      <c r="J2452" s="5">
+        <v>46252.445138888892</v>
+      </c>
+      <c r="K2452">
+        <v>8</v>
+      </c>
+      <c r="L2452">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2453" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2453">
+        <v>35203657</v>
+      </c>
+      <c r="B2453" s="5">
+        <v>46235</v>
+      </c>
+      <c r="C2453" t="s">
+        <v>155</v>
+      </c>
+      <c r="D2453" s="5">
+        <v>45412</v>
+      </c>
+      <c r="E2453" t="s">
+        <v>147</v>
+      </c>
+      <c r="F2453" t="s">
+        <v>31</v>
+      </c>
+      <c r="G2453" t="s">
+        <v>40</v>
+      </c>
+      <c r="H2453" t="s">
+        <v>41</v>
+      </c>
+      <c r="I2453" t="s">
+        <v>51</v>
+      </c>
+      <c r="J2453" s="5">
+        <v>46240.459722222222</v>
+      </c>
+      <c r="K2453">
+        <v>8</v>
+      </c>
+      <c r="L2453">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2454" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2454">
+        <v>30128809</v>
+      </c>
+      <c r="B2454" s="5">
+        <v>46251</v>
+      </c>
+      <c r="C2454" t="s">
+        <v>142</v>
+      </c>
+      <c r="D2454" s="5">
+        <v>44698</v>
+      </c>
+      <c r="E2454" t="s">
+        <v>149</v>
+      </c>
+      <c r="F2454" t="s">
+        <v>11</v>
+      </c>
+      <c r="G2454" t="s">
+        <v>49</v>
+      </c>
+      <c r="H2454" t="s">
+        <v>50</v>
+      </c>
+      <c r="I2454" t="s">
+        <v>51</v>
+      </c>
+      <c r="J2454" s="5">
+        <v>46252.379166666666</v>
+      </c>
+      <c r="K2454">
+        <v>8</v>
+      </c>
+      <c r="L2454">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2455" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2455">
+        <v>20173983</v>
+      </c>
+      <c r="B2455" s="5">
+        <v>46239</v>
+      </c>
+      <c r="C2455" t="s">
+        <v>142</v>
+      </c>
+      <c r="D2455" s="5">
+        <v>45874</v>
+      </c>
+      <c r="E2455" t="s">
+        <v>150</v>
+      </c>
+      <c r="F2455" t="s">
+        <v>16</v>
+      </c>
+      <c r="G2455" t="s">
+        <v>20</v>
+      </c>
+      <c r="H2455" t="s">
+        <v>21</v>
+      </c>
+      <c r="I2455" t="s">
+        <v>51</v>
+      </c>
+      <c r="J2455" s="5">
+        <v>46244.348611111112</v>
+      </c>
+      <c r="K2455">
+        <v>8</v>
+      </c>
+      <c r="L2455">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2456" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2456">
+        <v>20208176</v>
+      </c>
+      <c r="B2456" s="5">
+        <v>46245</v>
+      </c>
+      <c r="C2456" t="s">
+        <v>103</v>
+      </c>
+      <c r="D2456" s="5">
+        <v>46123</v>
+      </c>
+      <c r="E2456" t="s">
+        <v>153</v>
+      </c>
+      <c r="F2456" t="s">
+        <v>16</v>
+      </c>
+      <c r="G2456" t="s">
+        <v>20</v>
+      </c>
+      <c r="H2456" t="s">
+        <v>108</v>
+      </c>
+      <c r="I2456" t="s">
+        <v>51</v>
+      </c>
+      <c r="J2456" s="5">
+        <v>46252.341666666667</v>
+      </c>
+      <c r="K2456">
+        <v>8</v>
+      </c>
+      <c r="L2456">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2457" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2457">
+        <v>21121255</v>
+      </c>
+      <c r="B2457" s="5">
+        <v>46235</v>
+      </c>
+      <c r="C2457" t="s">
+        <v>23</v>
+      </c>
+      <c r="D2457" s="5">
+        <v>45655</v>
+      </c>
+      <c r="E2457" t="s">
+        <v>150</v>
+      </c>
+      <c r="F2457" t="s">
+        <v>16</v>
+      </c>
+      <c r="G2457" t="s">
+        <v>54</v>
+      </c>
+      <c r="H2457" t="s">
+        <v>55</v>
+      </c>
+      <c r="I2457" t="s">
+        <v>51</v>
+      </c>
+      <c r="J2457" s="5">
+        <v>46240.337500000001</v>
+      </c>
+      <c r="K2457">
+        <v>8</v>
+      </c>
+      <c r="L2457">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2458" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2458">
+        <v>21130522</v>
+      </c>
+      <c r="B2458" s="5">
+        <v>46236</v>
+      </c>
+      <c r="C2458" t="s">
+        <v>142</v>
+      </c>
+      <c r="D2458" s="5">
+        <v>45718</v>
+      </c>
+      <c r="E2458" t="s">
+        <v>150</v>
+      </c>
+      <c r="F2458" t="s">
+        <v>16</v>
+      </c>
+      <c r="G2458" t="s">
+        <v>54</v>
+      </c>
+      <c r="H2458" t="s">
+        <v>78</v>
+      </c>
+      <c r="I2458" t="s">
+        <v>51</v>
+      </c>
+      <c r="J2458" s="5">
+        <v>46242.395138888889</v>
+      </c>
+      <c r="K2458">
+        <v>8</v>
+      </c>
+      <c r="L2458">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2459" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2459">
+        <v>21139305</v>
+      </c>
+      <c r="B2459" s="5">
+        <v>46243</v>
+      </c>
+      <c r="C2459" t="s">
+        <v>23</v>
+      </c>
+      <c r="D2459" s="5">
+        <v>45817</v>
+      </c>
+      <c r="E2459" t="s">
+        <v>150</v>
+      </c>
+      <c r="F2459" t="s">
+        <v>16</v>
+      </c>
+      <c r="G2459" t="s">
+        <v>54</v>
+      </c>
+      <c r="H2459" t="s">
+        <v>55</v>
+      </c>
+      <c r="I2459" t="s">
+        <v>51</v>
+      </c>
+      <c r="J2459" s="5">
+        <v>46245.345833333333</v>
+      </c>
+      <c r="K2459">
+        <v>8</v>
+      </c>
+      <c r="L2459">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2460" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2460">
+        <v>21152123</v>
+      </c>
+      <c r="B2460" s="5">
+        <v>46235</v>
+      </c>
+      <c r="C2460" t="s">
+        <v>62</v>
+      </c>
+      <c r="D2460" s="5">
+        <v>45990</v>
+      </c>
+      <c r="E2460" t="s">
+        <v>151</v>
+      </c>
+      <c r="F2460" t="s">
+        <v>16</v>
+      </c>
+      <c r="G2460" t="s">
+        <v>54</v>
+      </c>
+      <c r="H2460" t="s">
+        <v>55</v>
+      </c>
+      <c r="I2460" t="s">
+        <v>51</v>
+      </c>
+      <c r="J2460" s="5">
+        <v>46239.370138888888</v>
+      </c>
+      <c r="K2460">
+        <v>8</v>
+      </c>
+      <c r="L2460">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2461" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2461">
+        <v>31031628</v>
+      </c>
+      <c r="B2461" s="5">
+        <v>46250</v>
+      </c>
+      <c r="C2461" t="s">
+        <v>142</v>
+      </c>
+      <c r="D2461" s="5">
+        <v>43815</v>
+      </c>
+      <c r="E2461" t="s">
+        <v>149</v>
+      </c>
+      <c r="F2461" t="s">
+        <v>31</v>
+      </c>
+      <c r="G2461" t="s">
+        <v>45</v>
+      </c>
+      <c r="H2461" t="s">
+        <v>46</v>
+      </c>
+      <c r="I2461" t="s">
+        <v>51</v>
+      </c>
+      <c r="J2461" s="5">
+        <v>46238.675000000003</v>
+      </c>
+      <c r="K2461">
+        <v>8</v>
+      </c>
+      <c r="L2461">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2462" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2462">
+        <v>30116557</v>
+      </c>
+      <c r="B2462" s="5">
+        <v>46243</v>
+      </c>
+      <c r="C2462" t="s">
+        <v>144</v>
+      </c>
+      <c r="D2462" s="5">
+        <v>44236</v>
+      </c>
+      <c r="E2462" t="s">
+        <v>149</v>
+      </c>
+      <c r="F2462" t="s">
+        <v>11</v>
+      </c>
+      <c r="G2462" t="s">
+        <v>49</v>
+      </c>
+      <c r="H2462" t="s">
+        <v>52</v>
+      </c>
+      <c r="I2462" t="s">
+        <v>30</v>
+      </c>
+      <c r="J2462" s="5">
+        <v>46245.487500000003</v>
+      </c>
+      <c r="K2462">
+        <v>8</v>
+      </c>
+      <c r="L2462">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2463" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2463">
+        <v>2161724</v>
+      </c>
+      <c r="B2463" s="5">
+        <v>46244</v>
+      </c>
+      <c r="C2463" t="s">
+        <v>142</v>
+      </c>
+      <c r="D2463" s="5">
+        <v>45757</v>
+      </c>
+      <c r="E2463" t="s">
+        <v>150</v>
+      </c>
+      <c r="F2463" t="s">
+        <v>11</v>
+      </c>
+      <c r="G2463" t="s">
+        <v>38</v>
+      </c>
+      <c r="H2463" t="s">
+        <v>29</v>
+      </c>
+      <c r="I2463" t="s">
+        <v>30</v>
+      </c>
+      <c r="J2463" s="5">
+        <v>46240.443749999999</v>
+      </c>
+      <c r="K2463">
+        <v>8</v>
+      </c>
+      <c r="L2463">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2464" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2464">
+        <v>20186092</v>
+      </c>
+      <c r="B2464" s="5">
+        <v>46241</v>
+      </c>
+      <c r="C2464" t="s">
+        <v>62</v>
+      </c>
+      <c r="D2464" s="5">
+        <v>45968</v>
+      </c>
+      <c r="E2464" t="s">
+        <v>152</v>
+      </c>
+      <c r="F2464" t="s">
+        <v>16</v>
+      </c>
+      <c r="G2464" t="s">
+        <v>20</v>
+      </c>
+      <c r="H2464" t="s">
+        <v>21</v>
+      </c>
+      <c r="I2464" t="s">
+        <v>30</v>
+      </c>
+      <c r="J2464" s="5">
+        <v>46245.318749999999</v>
+      </c>
+      <c r="K2464">
+        <v>8</v>
+      </c>
+      <c r="L2464">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2465" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2465">
+        <v>20200425</v>
+      </c>
+      <c r="B2465" s="5">
+        <v>46244</v>
+      </c>
+      <c r="C2465" t="s">
+        <v>103</v>
+      </c>
+      <c r="D2465" s="5">
+        <v>46063</v>
+      </c>
+      <c r="E2465" t="s">
+        <v>151</v>
+      </c>
+      <c r="F2465" t="s">
+        <v>16</v>
+      </c>
+      <c r="G2465" t="s">
+        <v>20</v>
+      </c>
+      <c r="H2465" t="s">
+        <v>108</v>
+      </c>
+      <c r="I2465" t="s">
+        <v>30</v>
+      </c>
+      <c r="J2465" s="5">
+        <v>46251.323611111111</v>
+      </c>
+      <c r="K2465">
+        <v>8</v>
+      </c>
+      <c r="L2465">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2466" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2466">
+        <v>33020703</v>
+      </c>
+      <c r="B2466" s="5">
+        <v>46242</v>
+      </c>
+      <c r="C2466" t="s">
+        <v>23</v>
+      </c>
+      <c r="D2466" s="5">
+        <v>45696</v>
+      </c>
+      <c r="E2466" t="s">
+        <v>150</v>
+      </c>
+      <c r="F2466" t="s">
+        <v>31</v>
+      </c>
+      <c r="G2466" t="s">
+        <v>43</v>
+      </c>
+      <c r="H2466" t="s">
+        <v>44</v>
+      </c>
+      <c r="I2466" t="s">
+        <v>30</v>
+      </c>
+      <c r="J2466" s="5">
+        <v>46238.373611111114</v>
+      </c>
+      <c r="K2466">
+        <v>8</v>
+      </c>
+      <c r="L2466">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2467" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2467">
+        <v>45138971</v>
+      </c>
+      <c r="B2467" s="5">
+        <v>46244</v>
+      </c>
+      <c r="C2467" t="s">
+        <v>142</v>
+      </c>
+      <c r="D2467" s="5">
+        <v>43809</v>
+      </c>
+      <c r="E2467" t="s">
+        <v>149</v>
+      </c>
+      <c r="F2467" t="s">
+        <v>31</v>
+      </c>
+      <c r="G2467" t="s">
+        <v>32</v>
+      </c>
+      <c r="H2467" t="s">
+        <v>35</v>
+      </c>
+      <c r="I2467" t="s">
+        <v>19</v>
+      </c>
+      <c r="J2467" s="5">
+        <v>46237.408333333333</v>
+      </c>
+      <c r="K2467">
+        <v>8</v>
+      </c>
+      <c r="L2467">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2468" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2468">
+        <v>45406101</v>
+      </c>
+      <c r="B2468" s="5">
+        <v>46241</v>
+      </c>
+      <c r="C2468" t="s">
+        <v>62</v>
+      </c>
+      <c r="D2468" s="5">
+        <v>45784</v>
+      </c>
+      <c r="E2468" t="s">
+        <v>150</v>
+      </c>
+      <c r="F2468" t="s">
+        <v>31</v>
+      </c>
+      <c r="G2468" t="s">
+        <v>32</v>
+      </c>
+      <c r="H2468" t="s">
+        <v>35</v>
+      </c>
+      <c r="I2468" t="s">
+        <v>19</v>
+      </c>
+      <c r="J2468" s="5">
+        <v>46245.353472222225</v>
+      </c>
+      <c r="K2468">
+        <v>8</v>
+      </c>
+      <c r="L2468">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2469" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2469">
+        <v>45414632</v>
+      </c>
+      <c r="B2469" s="5">
+        <v>46238</v>
+      </c>
+      <c r="C2469" t="s">
+        <v>62</v>
+      </c>
+      <c r="D2469" s="5">
+        <v>45904</v>
+      </c>
+      <c r="E2469" t="s">
+        <v>152</v>
+      </c>
+      <c r="F2469" t="s">
+        <v>31</v>
+      </c>
+      <c r="G2469" t="s">
+        <v>32</v>
+      </c>
+      <c r="H2469" t="s">
+        <v>109</v>
+      </c>
+      <c r="I2469" t="s">
+        <v>19</v>
+      </c>
+      <c r="J2469" s="5">
+        <v>46240.42291666667</v>
+      </c>
+      <c r="K2469">
+        <v>8</v>
+      </c>
+      <c r="L2469">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2470" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2470">
+        <v>35177422</v>
+      </c>
+      <c r="B2470" s="5">
+        <v>46237</v>
+      </c>
+      <c r="C2470" t="s">
+        <v>142</v>
+      </c>
+      <c r="D2470" s="5">
+        <v>44715</v>
+      </c>
+      <c r="E2470" t="s">
+        <v>149</v>
+      </c>
+      <c r="F2470" t="s">
+        <v>31</v>
+      </c>
+      <c r="G2470" t="s">
+        <v>40</v>
+      </c>
+      <c r="H2470" t="s">
+        <v>41</v>
+      </c>
+      <c r="I2470" t="s">
+        <v>19</v>
+      </c>
+      <c r="J2470" s="5">
+        <v>46238.440972222219</v>
+      </c>
+      <c r="K2470">
+        <v>8</v>
+      </c>
+      <c r="L2470">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2471" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2471">
+        <v>1942150</v>
+      </c>
+      <c r="B2471" s="5">
+        <v>46247</v>
+      </c>
+      <c r="C2471" t="s">
+        <v>142</v>
+      </c>
+      <c r="D2471" s="5">
+        <v>45182</v>
+      </c>
+      <c r="E2471" t="s">
+        <v>147</v>
+      </c>
+      <c r="F2471" t="s">
+        <v>11</v>
+      </c>
+      <c r="G2471" t="s">
+        <v>28</v>
+      </c>
+      <c r="H2471" t="s">
+        <v>34</v>
+      </c>
+      <c r="I2471" t="s">
+        <v>19</v>
+      </c>
+      <c r="J2471" s="5">
+        <v>46245.484722222223</v>
+      </c>
+      <c r="K2471">
+        <v>8</v>
+      </c>
+      <c r="L2471">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2472" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2472">
+        <v>2069010</v>
+      </c>
+      <c r="B2472" s="5">
+        <v>46244</v>
+      </c>
+      <c r="C2472" t="s">
+        <v>155</v>
+      </c>
+      <c r="D2472" s="5">
+        <v>44905</v>
+      </c>
+      <c r="E2472" t="s">
+        <v>149</v>
+      </c>
+      <c r="F2472" t="s">
+        <v>11</v>
+      </c>
+      <c r="G2472" t="s">
+        <v>28</v>
+      </c>
+      <c r="H2472" t="s">
+        <v>34</v>
+      </c>
+      <c r="I2472" t="s">
+        <v>19</v>
+      </c>
+      <c r="J2472" s="5">
+        <v>46240.675694444442</v>
+      </c>
+      <c r="K2472">
+        <v>8</v>
+      </c>
+      <c r="L2472">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2473" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2473">
+        <v>21138508</v>
+      </c>
+      <c r="B2473" s="5">
+        <v>46236</v>
+      </c>
+      <c r="C2473" t="s">
+        <v>62</v>
+      </c>
+      <c r="D2473" s="5">
+        <v>45810</v>
+      </c>
+      <c r="E2473" t="s">
+        <v>150</v>
+      </c>
+      <c r="F2473" t="s">
+        <v>16</v>
+      </c>
+      <c r="G2473" t="s">
+        <v>54</v>
+      </c>
+      <c r="H2473" t="s">
+        <v>55</v>
+      </c>
+      <c r="I2473" t="s">
+        <v>19</v>
+      </c>
+      <c r="J2473" s="5">
+        <v>46239.743055555555</v>
+      </c>
+      <c r="K2473">
+        <v>8</v>
+      </c>
+      <c r="L2473">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2474" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2474">
+        <v>50192241</v>
+      </c>
+      <c r="B2474" s="5">
+        <v>46240</v>
+      </c>
+      <c r="C2474" t="s">
+        <v>62</v>
+      </c>
+      <c r="D2474" s="5">
+        <v>45997</v>
+      </c>
+      <c r="E2474" t="s">
+        <v>151</v>
+      </c>
+      <c r="F2474" t="s">
+        <v>11</v>
+      </c>
+      <c r="G2474" t="s">
+        <v>12</v>
+      </c>
+      <c r="H2474" t="s">
+        <v>13</v>
+      </c>
+      <c r="I2474" t="s">
+        <v>19</v>
+      </c>
+      <c r="J2474" s="5">
+        <v>46242.350694444445</v>
+      </c>
+      <c r="K2474">
+        <v>8</v>
+      </c>
+      <c r="L2474">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2475" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2475">
+        <v>45434859</v>
+      </c>
+      <c r="B2475" s="5">
+        <v>46243</v>
+      </c>
+      <c r="C2475" t="s">
+        <v>103</v>
+      </c>
+      <c r="D2475" s="5">
+        <v>46182</v>
+      </c>
+      <c r="E2475" t="s">
+        <v>148</v>
+      </c>
+      <c r="F2475" t="s">
+        <v>31</v>
+      </c>
+      <c r="G2475" t="s">
+        <v>32</v>
+      </c>
+      <c r="H2475" t="s">
+        <v>37</v>
+      </c>
+      <c r="I2475" t="s">
+        <v>47</v>
+      </c>
+      <c r="J2475" s="5">
+        <v>46248.363888888889</v>
+      </c>
+      <c r="K2475">
+        <v>8</v>
+      </c>
+      <c r="L2475">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2476" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2476">
+        <v>20165258</v>
+      </c>
+      <c r="B2476" s="5">
+        <v>46239</v>
+      </c>
+      <c r="C2476" t="s">
+        <v>142</v>
+      </c>
+      <c r="D2476" s="5">
+        <v>45813</v>
+      </c>
+      <c r="E2476" t="s">
+        <v>150</v>
+      </c>
+      <c r="F2476" t="s">
+        <v>16</v>
+      </c>
+      <c r="G2476" t="s">
+        <v>20</v>
+      </c>
+      <c r="H2476" t="s">
+        <v>57</v>
+      </c>
+      <c r="I2476" t="s">
+        <v>47</v>
+      </c>
+      <c r="J2476" s="5">
+        <v>46244.356944444444</v>
+      </c>
+      <c r="K2476">
+        <v>8</v>
+      </c>
+      <c r="L2476">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2477" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2477">
+        <v>20211807</v>
+      </c>
+      <c r="B2477" s="5">
+        <v>46242</v>
+      </c>
+      <c r="C2477" t="s">
+        <v>103</v>
+      </c>
+      <c r="D2477" s="5">
+        <v>46150</v>
+      </c>
+      <c r="E2477" t="s">
+        <v>153</v>
+      </c>
+      <c r="F2477" t="s">
+        <v>16</v>
+      </c>
+      <c r="G2477" t="s">
+        <v>20</v>
+      </c>
+      <c r="H2477" t="s">
+        <v>21</v>
+      </c>
+      <c r="I2477" t="s">
+        <v>47</v>
+      </c>
+      <c r="J2477" s="5">
+        <v>46248.367361111108</v>
+      </c>
+      <c r="K2477">
+        <v>8</v>
+      </c>
+      <c r="L2477">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2478" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2478">
+        <v>20215175</v>
+      </c>
+      <c r="B2478" s="5">
+        <v>46239</v>
+      </c>
+      <c r="C2478" t="s">
+        <v>103</v>
+      </c>
+      <c r="D2478" s="5">
+        <v>46178</v>
+      </c>
+      <c r="E2478" t="s">
+        <v>148</v>
+      </c>
+      <c r="F2478" t="s">
+        <v>16</v>
+      </c>
+      <c r="G2478" t="s">
+        <v>20</v>
+      </c>
+      <c r="H2478" t="s">
+        <v>21</v>
+      </c>
+      <c r="I2478" t="s">
+        <v>47</v>
+      </c>
+      <c r="J2478" s="5">
+        <v>46242.384722222225</v>
+      </c>
+      <c r="K2478">
+        <v>8</v>
+      </c>
+      <c r="L2478">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2479" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2479">
+        <v>21162553</v>
+      </c>
+      <c r="B2479" s="5">
+        <v>46242</v>
+      </c>
+      <c r="C2479" t="s">
+        <v>103</v>
+      </c>
+      <c r="D2479" s="5">
+        <v>46150</v>
+      </c>
+      <c r="E2479" t="s">
+        <v>153</v>
+      </c>
+      <c r="F2479" t="s">
+        <v>16</v>
+      </c>
+      <c r="G2479" t="s">
+        <v>54</v>
+      </c>
+      <c r="H2479" t="s">
+        <v>78</v>
+      </c>
+      <c r="I2479" t="s">
+        <v>47</v>
+      </c>
+      <c r="J2479" s="5">
+        <v>46251.644444444442</v>
+      </c>
+      <c r="K2479">
+        <v>8</v>
+      </c>
+      <c r="L2479">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2480" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2480">
+        <v>50135872</v>
+      </c>
+      <c r="B2480" s="5">
+        <v>46248</v>
+      </c>
+      <c r="C2480" t="s">
+        <v>85</v>
+      </c>
+      <c r="D2480" s="5">
+        <v>44879</v>
+      </c>
+      <c r="E2480" t="s">
+        <v>149</v>
+      </c>
+      <c r="F2480" t="s">
+        <v>11</v>
+      </c>
+      <c r="G2480" t="s">
+        <v>12</v>
+      </c>
+      <c r="H2480" t="s">
+        <v>13</v>
+      </c>
+      <c r="I2480" t="s">
+        <v>47</v>
+      </c>
+      <c r="J2480" s="5">
+        <v>46248.418749999997</v>
+      </c>
+      <c r="K2480">
+        <v>8</v>
+      </c>
+      <c r="L2480">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2481" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2481">
+        <v>50203210</v>
+      </c>
+      <c r="B2481" s="5">
+        <v>46240</v>
+      </c>
+      <c r="C2481" t="s">
+        <v>103</v>
+      </c>
+      <c r="D2481" s="5">
+        <v>46179</v>
+      </c>
+      <c r="E2481" t="s">
+        <v>148</v>
+      </c>
+      <c r="F2481" t="s">
+        <v>11</v>
+      </c>
+      <c r="G2481" t="s">
+        <v>12</v>
+      </c>
+      <c r="H2481" t="s">
+        <v>124</v>
+      </c>
+      <c r="I2481" t="s">
+        <v>47</v>
+      </c>
+      <c r="J2481" s="5">
+        <v>46242.368750000001</v>
+      </c>
+      <c r="K2481">
+        <v>8</v>
+      </c>
+      <c r="L2481">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2482" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2482">
+        <v>45408413</v>
+      </c>
+      <c r="B2482" s="5">
+        <v>46242</v>
+      </c>
+      <c r="C2482" t="s">
+        <v>62</v>
+      </c>
+      <c r="D2482" s="5">
+        <v>45816</v>
+      </c>
+      <c r="E2482" t="s">
+        <v>150</v>
+      </c>
+      <c r="F2482" t="s">
+        <v>31</v>
+      </c>
+      <c r="G2482" t="s">
+        <v>32</v>
+      </c>
+      <c r="H2482" t="s">
+        <v>35</v>
+      </c>
+      <c r="I2482" t="s">
+        <v>141</v>
+      </c>
+      <c r="J2482" s="5">
+        <v>46249.368750000001</v>
+      </c>
+      <c r="K2482">
+        <v>8</v>
+      </c>
+      <c r="L2482">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2483" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2483">
+        <v>60015215</v>
+      </c>
+      <c r="B2483" s="5">
+        <v>46235</v>
+      </c>
+      <c r="C2483" t="s">
+        <v>62</v>
+      </c>
+      <c r="D2483" s="5">
+        <v>46051</v>
+      </c>
+      <c r="E2483" t="s">
+        <v>151</v>
+      </c>
+      <c r="F2483" t="s">
+        <v>31</v>
+      </c>
+      <c r="G2483" t="s">
+        <v>63</v>
+      </c>
+      <c r="H2483" t="s">
+        <v>89</v>
+      </c>
+      <c r="I2483" t="s">
+        <v>141</v>
+      </c>
+      <c r="J2483" s="5">
+        <v>46238.281944444447</v>
+      </c>
+      <c r="K2483">
+        <v>8</v>
+      </c>
+      <c r="L2483">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2484" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2484">
+        <v>21162297</v>
+      </c>
+      <c r="B2484" s="5">
+        <v>46240</v>
+      </c>
+      <c r="C2484" t="s">
+        <v>103</v>
+      </c>
+      <c r="D2484" s="5">
+        <v>46148</v>
+      </c>
+      <c r="E2484" t="s">
+        <v>153</v>
+      </c>
+      <c r="F2484" t="s">
+        <v>16</v>
+      </c>
+      <c r="G2484" t="s">
+        <v>54</v>
+      </c>
+      <c r="H2484" t="s">
+        <v>55</v>
+      </c>
+      <c r="I2484" t="s">
+        <v>141</v>
+      </c>
+      <c r="J2484" s="5">
+        <v>46244.288888888892</v>
+      </c>
+      <c r="K2484">
+        <v>8</v>
+      </c>
+      <c r="L2484">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2485" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2485">
+        <v>31169198</v>
+      </c>
+      <c r="B2485" s="5">
+        <v>46235</v>
+      </c>
+      <c r="C2485" t="s">
+        <v>62</v>
+      </c>
+      <c r="D2485" s="5">
+        <v>45777</v>
+      </c>
+      <c r="E2485" t="s">
+        <v>150</v>
+      </c>
+      <c r="F2485" t="s">
+        <v>31</v>
+      </c>
+      <c r="G2485" t="s">
+        <v>45</v>
+      </c>
+      <c r="H2485" t="s">
+        <v>46</v>
+      </c>
+      <c r="I2485" t="s">
+        <v>141</v>
+      </c>
+      <c r="J2485" s="5">
+        <v>46238.273611111108</v>
+      </c>
+      <c r="K2485">
+        <v>8</v>
+      </c>
+      <c r="L2485">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2486" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2486">
+        <v>50201059</v>
+      </c>
+      <c r="B2486" s="5">
+        <v>46236</v>
+      </c>
+      <c r="C2486" t="s">
+        <v>103</v>
+      </c>
+      <c r="D2486" s="5">
+        <v>46144</v>
+      </c>
+      <c r="E2486" t="s">
+        <v>153</v>
+      </c>
+      <c r="F2486" t="s">
+        <v>11</v>
+      </c>
+      <c r="G2486" t="s">
+        <v>12</v>
+      </c>
+      <c r="H2486" t="s">
+        <v>13</v>
+      </c>
+      <c r="I2486" t="s">
+        <v>141</v>
+      </c>
+      <c r="J2486" s="5">
+        <v>46238.288888888892</v>
+      </c>
+      <c r="K2486">
+        <v>8</v>
+      </c>
+      <c r="L2486">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2487" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2487">
+        <v>45351272</v>
+      </c>
+      <c r="B2487" s="5">
+        <v>46235</v>
+      </c>
+      <c r="C2487" t="s">
+        <v>62</v>
+      </c>
+      <c r="D2487" s="5">
+        <v>45108</v>
+      </c>
+      <c r="E2487" t="s">
+        <v>149</v>
+      </c>
+      <c r="F2487" t="s">
+        <v>31</v>
+      </c>
+      <c r="G2487" t="s">
+        <v>32</v>
+      </c>
+      <c r="H2487" t="s">
+        <v>35</v>
+      </c>
+      <c r="I2487" t="s">
+        <v>22</v>
+      </c>
+      <c r="J2487" s="5">
+        <v>46239.379861111112</v>
+      </c>
+      <c r="K2487">
+        <v>8</v>
+      </c>
+      <c r="L2487">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2488" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2488">
+        <v>45428028</v>
+      </c>
+      <c r="B2488" s="5">
+        <v>46241</v>
+      </c>
+      <c r="C2488" t="s">
+        <v>103</v>
+      </c>
+      <c r="D2488" s="5">
+        <v>46088</v>
+      </c>
+      <c r="E2488" t="s">
+        <v>153</v>
+      </c>
+      <c r="F2488" t="s">
+        <v>31</v>
+      </c>
+      <c r="G2488" t="s">
+        <v>32</v>
+      </c>
+      <c r="H2488" t="s">
+        <v>68</v>
+      </c>
+      <c r="I2488" t="s">
+        <v>22</v>
+      </c>
+      <c r="J2488" s="5">
+        <v>46246.365277777775</v>
+      </c>
+      <c r="K2488">
+        <v>8</v>
+      </c>
+      <c r="L2488">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2489" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2489">
+        <v>35229881</v>
+      </c>
+      <c r="B2489" s="5">
+        <v>46241</v>
+      </c>
+      <c r="C2489" t="s">
+        <v>62</v>
+      </c>
+      <c r="D2489" s="5">
+        <v>45876</v>
+      </c>
+      <c r="E2489" t="s">
+        <v>150</v>
+      </c>
+      <c r="F2489" t="s">
+        <v>31</v>
+      </c>
+      <c r="G2489" t="s">
+        <v>40</v>
+      </c>
+      <c r="H2489" t="s">
+        <v>121</v>
+      </c>
+      <c r="I2489" t="s">
+        <v>22</v>
+      </c>
+      <c r="J2489" s="5">
+        <v>46251.649305555555</v>
+      </c>
+      <c r="K2489">
+        <v>8</v>
+      </c>
+      <c r="L2489">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2490" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2490">
+        <v>23003684</v>
+      </c>
+      <c r="B2490" s="5">
+        <v>46247</v>
+      </c>
+      <c r="C2490" t="s">
+        <v>15</v>
+      </c>
+      <c r="D2490" s="5">
+        <v>46035</v>
+      </c>
+      <c r="E2490" t="s">
+        <v>151</v>
+      </c>
+      <c r="F2490" t="s">
+        <v>16</v>
+      </c>
+      <c r="G2490" t="s">
+        <v>17</v>
+      </c>
+      <c r="H2490" t="s">
+        <v>18</v>
+      </c>
+      <c r="I2490" t="s">
+        <v>22</v>
+      </c>
+      <c r="J2490" s="5">
+        <v>46252.353472222225</v>
+      </c>
+      <c r="K2490">
+        <v>8</v>
+      </c>
+      <c r="L2490">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2491" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2491">
+        <v>2119547</v>
+      </c>
+      <c r="B2491" s="5">
+        <v>46239</v>
+      </c>
+      <c r="C2491" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2491" s="5">
+        <v>45327</v>
+      </c>
+      <c r="E2491" t="s">
+        <v>147</v>
+      </c>
+      <c r="F2491" t="s">
+        <v>11</v>
+      </c>
+      <c r="G2491" t="s">
+        <v>38</v>
+      </c>
+      <c r="H2491" t="s">
+        <v>60</v>
+      </c>
+      <c r="I2491" t="s">
+        <v>22</v>
+      </c>
+      <c r="J2491" s="5">
+        <v>46240.333333333336</v>
+      </c>
+      <c r="K2491">
+        <v>8</v>
+      </c>
+      <c r="L2491">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2492" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2492">
+        <v>20161585</v>
+      </c>
+      <c r="B2492" s="5">
+        <v>46243</v>
+      </c>
+      <c r="C2492" t="s">
+        <v>23</v>
+      </c>
+      <c r="D2492" s="5">
+        <v>45786</v>
+      </c>
+      <c r="E2492" t="s">
+        <v>150</v>
+      </c>
+      <c r="F2492" t="s">
+        <v>16</v>
+      </c>
+      <c r="G2492" t="s">
+        <v>20</v>
+      </c>
+      <c r="H2492" t="s">
+        <v>21</v>
+      </c>
+      <c r="I2492" t="s">
+        <v>22</v>
+      </c>
+      <c r="J2492" s="5">
+        <v>46248.392361111109</v>
+      </c>
+      <c r="K2492">
+        <v>8</v>
+      </c>
+      <c r="L2492">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2493" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2493">
+        <v>22006846</v>
+      </c>
+      <c r="B2493" s="5">
+        <v>46243</v>
+      </c>
+      <c r="C2493" t="s">
+        <v>103</v>
+      </c>
+      <c r="D2493" s="5">
+        <v>46121</v>
+      </c>
+      <c r="E2493" t="s">
+        <v>153</v>
+      </c>
+      <c r="F2493" t="s">
+        <v>16</v>
+      </c>
+      <c r="G2493" t="s">
+        <v>100</v>
+      </c>
+      <c r="H2493" t="s">
+        <v>101</v>
+      </c>
+      <c r="I2493" t="s">
+        <v>22</v>
+      </c>
+      <c r="J2493" s="5">
+        <v>46245.35833333333</v>
+      </c>
+      <c r="K2493">
+        <v>8</v>
+      </c>
+      <c r="L2493">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2494" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2494">
+        <v>21132665</v>
+      </c>
+      <c r="B2494" s="5">
+        <v>46238</v>
+      </c>
+      <c r="C2494" t="s">
+        <v>23</v>
+      </c>
+      <c r="D2494" s="5">
+        <v>45751</v>
+      </c>
+      <c r="E2494" t="s">
+        <v>150</v>
+      </c>
+      <c r="F2494" t="s">
+        <v>16</v>
+      </c>
+      <c r="G2494" t="s">
+        <v>54</v>
+      </c>
+      <c r="H2494" t="s">
+        <v>78</v>
+      </c>
+      <c r="I2494" t="s">
+        <v>22</v>
+      </c>
+      <c r="J2494" s="5">
+        <v>46241.345138888886</v>
+      </c>
+      <c r="K2494">
+        <v>8</v>
+      </c>
+      <c r="L2494">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2495" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2495">
+        <v>31171740</v>
+      </c>
+      <c r="B2495" s="5">
+        <v>46241</v>
+      </c>
+      <c r="C2495" t="s">
+        <v>62</v>
+      </c>
+      <c r="D2495" s="5">
+        <v>45815</v>
+      </c>
+      <c r="E2495" t="s">
+        <v>150</v>
+      </c>
+      <c r="F2495" t="s">
+        <v>31</v>
+      </c>
+      <c r="G2495" t="s">
+        <v>45</v>
+      </c>
+      <c r="H2495" t="s">
+        <v>102</v>
+      </c>
+      <c r="I2495" t="s">
+        <v>22</v>
+      </c>
+      <c r="J2495" s="5">
+        <v>46248.631944444445</v>
+      </c>
+      <c r="K2495">
+        <v>8</v>
+      </c>
+      <c r="L2495">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2496" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2496">
+        <v>31190211</v>
+      </c>
+      <c r="B2496" s="5">
+        <v>46244</v>
+      </c>
+      <c r="C2496" t="s">
+        <v>62</v>
+      </c>
+      <c r="D2496" s="5">
+        <v>46032</v>
+      </c>
+      <c r="E2496" t="s">
+        <v>151</v>
+      </c>
+      <c r="F2496" t="s">
+        <v>31</v>
+      </c>
+      <c r="G2496" t="s">
+        <v>45</v>
+      </c>
+      <c r="H2496" t="s">
+        <v>75</v>
+      </c>
+      <c r="I2496" t="s">
+        <v>22</v>
+      </c>
+      <c r="J2496" s="5">
+        <v>46245.378472222219</v>
+      </c>
+      <c r="K2496">
+        <v>8</v>
+      </c>
+      <c r="L2496">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2497" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2497">
+        <v>50180725</v>
+      </c>
+      <c r="B2497" s="5">
+        <v>46237</v>
+      </c>
+      <c r="C2497" t="s">
+        <v>23</v>
+      </c>
+      <c r="D2497" s="5">
+        <v>45841</v>
+      </c>
+      <c r="E2497" t="s">
+        <v>150</v>
+      </c>
+      <c r="F2497" t="s">
+        <v>11</v>
+      </c>
+      <c r="G2497" t="s">
+        <v>12</v>
+      </c>
+      <c r="H2497" t="s">
+        <v>13</v>
+      </c>
+      <c r="I2497" t="s">
+        <v>22</v>
+      </c>
+      <c r="J2497" s="5">
+        <v>46239.384027777778</v>
+      </c>
+      <c r="K2497">
+        <v>8</v>
+      </c>
+      <c r="L2497">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2498" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2498">
+        <v>20174087</v>
+      </c>
+      <c r="B2498" s="5">
+        <v>46240</v>
+      </c>
+      <c r="C2498" t="s">
+        <v>144</v>
+      </c>
+      <c r="D2498" s="5">
+        <v>45875</v>
+      </c>
+      <c r="E2498" t="s">
+        <v>150</v>
+      </c>
+      <c r="F2498" t="s">
+        <v>16</v>
+      </c>
+      <c r="G2498" t="s">
+        <v>20</v>
+      </c>
+      <c r="H2498" t="s">
+        <v>57</v>
+      </c>
+      <c r="I2498" t="s">
+        <v>53</v>
+      </c>
+      <c r="J2498" s="5">
+        <v>46246.629861111112</v>
+      </c>
+      <c r="K2498">
+        <v>8</v>
+      </c>
+      <c r="L2498">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2499" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2499">
+        <v>20205819</v>
+      </c>
+      <c r="B2499" s="5">
+        <v>46238</v>
+      </c>
+      <c r="C2499" t="s">
+        <v>103</v>
+      </c>
+      <c r="D2499" s="5">
+        <v>46116</v>
+      </c>
+      <c r="E2499" t="s">
+        <v>153</v>
+      </c>
+      <c r="F2499" t="s">
+        <v>16</v>
+      </c>
+      <c r="G2499" t="s">
+        <v>20</v>
+      </c>
+      <c r="H2499" t="s">
+        <v>108</v>
+      </c>
+      <c r="I2499" t="s">
+        <v>53</v>
+      </c>
+      <c r="J2499" s="5">
+        <v>46241.370833333334</v>
+      </c>
+      <c r="K2499">
+        <v>8</v>
+      </c>
+      <c r="L2499">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2500" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2500">
+        <v>20211513</v>
+      </c>
+      <c r="B2500" s="5">
+        <v>46240</v>
+      </c>
+      <c r="C2500" t="s">
+        <v>103</v>
+      </c>
+      <c r="D2500" s="5">
+        <v>46148</v>
+      </c>
+      <c r="E2500" t="s">
+        <v>153</v>
+      </c>
+      <c r="F2500" t="s">
+        <v>16</v>
+      </c>
+      <c r="G2500" t="s">
+        <v>20</v>
+      </c>
+      <c r="H2500" t="s">
+        <v>21</v>
+      </c>
+      <c r="I2500" t="s">
+        <v>53</v>
+      </c>
+      <c r="J2500" s="5">
+        <v>46246.634722222225</v>
+      </c>
+      <c r="K2500">
+        <v>8</v>
+      </c>
+      <c r="L2500">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2501" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2501">
+        <v>21136075</v>
+      </c>
+      <c r="B2501" s="5">
+        <v>46239</v>
+      </c>
+      <c r="C2501" t="s">
+        <v>62</v>
+      </c>
+      <c r="D2501" s="5">
+        <v>45782</v>
+      </c>
+      <c r="E2501" t="s">
+        <v>150</v>
+      </c>
+      <c r="F2501" t="s">
+        <v>16</v>
+      </c>
+      <c r="G2501" t="s">
+        <v>54</v>
+      </c>
+      <c r="H2501" t="s">
+        <v>55</v>
+      </c>
+      <c r="I2501" t="s">
+        <v>53</v>
+      </c>
+      <c r="J2501" s="5">
+        <v>46245.673611111109</v>
+      </c>
+      <c r="K2501">
+        <v>8</v>
+      </c>
+      <c r="L2501">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2502" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2502">
+        <v>45405869</v>
+      </c>
+      <c r="B2502" s="5">
+        <v>46241</v>
+      </c>
+      <c r="C2502" t="s">
+        <v>23</v>
+      </c>
+      <c r="D2502" s="5">
+        <v>45784</v>
+      </c>
+      <c r="E2502" t="s">
+        <v>150</v>
+      </c>
+      <c r="F2502" t="s">
+        <v>31</v>
+      </c>
+      <c r="G2502" t="s">
+        <v>32</v>
+      </c>
+      <c r="H2502" t="s">
+        <v>93</v>
+      </c>
+      <c r="I2502" t="s">
+        <v>56</v>
+      </c>
+      <c r="J2502" s="5">
+        <v>46246.495833333334</v>
+      </c>
+      <c r="K2502">
+        <v>8</v>
+      </c>
+      <c r="L2502">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2503" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2503">
+        <v>20164547</v>
+      </c>
+      <c r="B2503" s="5">
+        <v>46235</v>
+      </c>
+      <c r="C2503" t="s">
+        <v>23</v>
+      </c>
+      <c r="D2503" s="5">
+        <v>45808</v>
+      </c>
+      <c r="E2503" t="s">
+        <v>150</v>
+      </c>
+      <c r="F2503" t="s">
+        <v>16</v>
+      </c>
+      <c r="G2503" t="s">
+        <v>20</v>
+      </c>
+      <c r="H2503" t="s">
+        <v>21</v>
+      </c>
+      <c r="I2503" t="s">
+        <v>56</v>
+      </c>
+      <c r="J2503" s="5">
+        <v>46240.696527777778</v>
+      </c>
+      <c r="K2503">
+        <v>8</v>
+      </c>
+      <c r="L2503">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2504" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2504">
+        <v>60006368</v>
+      </c>
+      <c r="B2504" s="5">
+        <v>46243</v>
+      </c>
+      <c r="C2504" t="s">
+        <v>62</v>
+      </c>
+      <c r="D2504" s="5">
+        <v>45725</v>
+      </c>
+      <c r="E2504" t="s">
+        <v>150</v>
+      </c>
+      <c r="F2504" t="s">
+        <v>31</v>
+      </c>
+      <c r="G2504" t="s">
+        <v>63</v>
+      </c>
+      <c r="H2504" t="s">
+        <v>64</v>
+      </c>
+      <c r="I2504" t="s">
+        <v>56</v>
+      </c>
+      <c r="J2504" s="5">
+        <v>46248.453472222223</v>
+      </c>
+      <c r="K2504">
+        <v>8</v>
+      </c>
+      <c r="L2504">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2505" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2505">
+        <v>60012848</v>
+      </c>
+      <c r="B2505" s="5">
+        <v>46244</v>
+      </c>
+      <c r="C2505" t="s">
+        <v>62</v>
+      </c>
+      <c r="D2505" s="5">
+        <v>45971</v>
+      </c>
+      <c r="E2505" t="s">
+        <v>152</v>
+      </c>
+      <c r="F2505" t="s">
+        <v>31</v>
+      </c>
+      <c r="G2505" t="s">
+        <v>63</v>
+      </c>
+      <c r="H2505" t="s">
+        <v>160</v>
+      </c>
+      <c r="I2505" t="s">
+        <v>56</v>
+      </c>
+      <c r="J2505" s="5">
+        <v>46251.47152777778</v>
+      </c>
+      <c r="K2505">
+        <v>8</v>
+      </c>
+      <c r="L2505">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2506" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2506">
+        <v>21119044</v>
+      </c>
+      <c r="B2506" s="5">
+        <v>46243</v>
+      </c>
+      <c r="C2506" t="s">
+        <v>23</v>
+      </c>
+      <c r="D2506" s="5">
+        <v>45574</v>
+      </c>
+      <c r="E2506" t="s">
+        <v>150</v>
+      </c>
+      <c r="F2506" t="s">
+        <v>16</v>
+      </c>
+      <c r="G2506" t="s">
+        <v>54</v>
+      </c>
+      <c r="H2506" t="s">
+        <v>55</v>
+      </c>
+      <c r="I2506" t="s">
+        <v>56</v>
+      </c>
+      <c r="J2506" s="5">
+        <v>46249.494444444441</v>
+      </c>
+      <c r="K2506">
+        <v>8</v>
+      </c>
+      <c r="L2506">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2507" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2507">
+        <v>21154663</v>
+      </c>
+      <c r="B2507" s="5">
+        <v>46242</v>
+      </c>
+      <c r="C2507" t="s">
+        <v>23</v>
+      </c>
+      <c r="D2507" s="5">
+        <v>46030</v>
+      </c>
+      <c r="E2507" t="s">
+        <v>151</v>
+      </c>
+      <c r="F2507" t="s">
+        <v>16</v>
+      </c>
+      <c r="G2507" t="s">
+        <v>54</v>
+      </c>
+      <c r="H2507" t="s">
+        <v>55</v>
+      </c>
+      <c r="I2507" t="s">
+        <v>56</v>
+      </c>
+      <c r="J2507" s="5">
+        <v>46248.445138888892</v>
+      </c>
+      <c r="K2507">
+        <v>8</v>
+      </c>
+      <c r="L2507">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2508" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2508">
+        <v>21160208</v>
+      </c>
+      <c r="B2508" s="5">
+        <v>46238</v>
+      </c>
+      <c r="C2508" t="s">
+        <v>103</v>
+      </c>
+      <c r="D2508" s="5">
+        <v>46116</v>
+      </c>
+      <c r="E2508" t="s">
+        <v>153</v>
+      </c>
+      <c r="F2508" t="s">
+        <v>16</v>
+      </c>
+      <c r="G2508" t="s">
+        <v>54</v>
+      </c>
+      <c r="H2508" t="s">
+        <v>55</v>
+      </c>
+      <c r="I2508" t="s">
+        <v>56</v>
+      </c>
+      <c r="J2508" s="5">
+        <v>46245.344444444447</v>
+      </c>
+      <c r="K2508">
+        <v>8</v>
+      </c>
+      <c r="L2508">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2509" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2509">
+        <v>31167510</v>
+      </c>
+      <c r="B2509" s="5">
+        <v>46244</v>
+      </c>
+      <c r="C2509" t="s">
+        <v>62</v>
+      </c>
+      <c r="D2509" s="5">
+        <v>45757</v>
+      </c>
+      <c r="E2509" t="s">
+        <v>150</v>
+      </c>
+      <c r="F2509" t="s">
+        <v>31</v>
+      </c>
+      <c r="G2509" t="s">
+        <v>45</v>
+      </c>
+      <c r="H2509" t="s">
+        <v>46</v>
+      </c>
+      <c r="I2509" t="s">
+        <v>56</v>
+      </c>
+      <c r="J2509" s="5">
+        <v>46249.461805555555</v>
+      </c>
+      <c r="K2509">
+        <v>8</v>
+      </c>
+      <c r="L2509">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2510" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2510">
+        <v>35131812</v>
+      </c>
+      <c r="B2510" s="5">
+        <v>46247</v>
+      </c>
+      <c r="C2510" t="s">
+        <v>23</v>
+      </c>
+      <c r="D2510" s="5">
+        <v>43934</v>
+      </c>
+      <c r="E2510" t="s">
+        <v>149</v>
+      </c>
+      <c r="F2510" t="s">
+        <v>31</v>
+      </c>
+      <c r="G2510" t="s">
+        <v>40</v>
+      </c>
+      <c r="H2510" t="s">
+        <v>41</v>
+      </c>
+      <c r="I2510" t="s">
+        <v>65</v>
+      </c>
+      <c r="J2510" s="5">
+        <v>46219.675000000003</v>
+      </c>
+      <c r="K2510">
+        <v>8</v>
+      </c>
+      <c r="L2510">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2511" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2511">
+        <v>35162212</v>
+      </c>
+      <c r="B2511" s="5">
+        <v>46235</v>
+      </c>
+      <c r="C2511" t="s">
+        <v>23</v>
+      </c>
+      <c r="D2511" s="5">
+        <v>44103</v>
+      </c>
+      <c r="E2511" t="s">
+        <v>149</v>
+      </c>
+      <c r="F2511" t="s">
+        <v>31</v>
+      </c>
+      <c r="G2511" t="s">
+        <v>40</v>
+      </c>
+      <c r="H2511" t="s">
+        <v>41</v>
+      </c>
+      <c r="I2511" t="s">
+        <v>65</v>
+      </c>
+      <c r="J2511" s="5">
+        <v>46211.500694444447</v>
+      </c>
+      <c r="K2511">
+        <v>8</v>
+      </c>
+      <c r="L2511">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2512" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2512">
+        <v>35165664</v>
+      </c>
+      <c r="B2512" s="5">
+        <v>46241</v>
+      </c>
+      <c r="C2512" t="s">
+        <v>23</v>
+      </c>
+      <c r="D2512" s="5">
+        <v>44262</v>
+      </c>
+      <c r="E2512" t="s">
+        <v>149</v>
+      </c>
+      <c r="F2512" t="s">
+        <v>31</v>
+      </c>
+      <c r="G2512" t="s">
+        <v>40</v>
+      </c>
+      <c r="H2512" t="s">
+        <v>41</v>
+      </c>
+      <c r="I2512" t="s">
+        <v>65</v>
+      </c>
+      <c r="J2512" s="5">
+        <v>46226.436805555553</v>
+      </c>
+      <c r="K2512">
+        <v>8</v>
+      </c>
+      <c r="L2512">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2513" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2513">
+        <v>2115842</v>
+      </c>
+      <c r="B2513" s="5">
+        <v>46243</v>
+      </c>
+      <c r="C2513" t="s">
+        <v>23</v>
+      </c>
+      <c r="D2513" s="5">
+        <v>45269</v>
+      </c>
+      <c r="E2513" t="s">
+        <v>147</v>
+      </c>
+      <c r="F2513" t="s">
+        <v>11</v>
+      </c>
+      <c r="G2513" t="s">
+        <v>28</v>
+      </c>
+      <c r="H2513" t="s">
+        <v>34</v>
+      </c>
+      <c r="I2513" t="s">
+        <v>65</v>
+      </c>
+      <c r="J2513" s="5">
+        <v>46221.49722222222</v>
+      </c>
+      <c r="K2513">
+        <v>8</v>
+      </c>
+      <c r="L2513">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2514" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2514">
+        <v>21133128</v>
+      </c>
+      <c r="B2514" s="5">
+        <v>46239</v>
+      </c>
+      <c r="C2514" t="s">
+        <v>62</v>
+      </c>
+      <c r="D2514" s="5">
+        <v>45752</v>
+      </c>
+      <c r="E2514" t="s">
+        <v>150</v>
+      </c>
+      <c r="F2514" t="s">
+        <v>16</v>
+      </c>
+      <c r="G2514" t="s">
+        <v>54</v>
+      </c>
+      <c r="H2514" t="s">
+        <v>55</v>
+      </c>
+      <c r="I2514" t="s">
+        <v>65</v>
+      </c>
+      <c r="J2514" s="5">
+        <v>46221.393055555556</v>
+      </c>
+      <c r="K2514">
+        <v>8</v>
+      </c>
+      <c r="L2514">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2515" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2515">
+        <v>30145077</v>
+      </c>
+      <c r="B2515" s="5">
+        <v>46235</v>
+      </c>
+      <c r="C2515" t="s">
+        <v>23</v>
+      </c>
+      <c r="D2515" s="5">
+        <v>45169</v>
+      </c>
+      <c r="E2515" t="s">
+        <v>147</v>
+      </c>
+      <c r="F2515" t="s">
+        <v>11</v>
+      </c>
+      <c r="G2515" t="s">
+        <v>49</v>
+      </c>
+      <c r="H2515" t="s">
+        <v>50</v>
+      </c>
+      <c r="I2515" t="s">
+        <v>59</v>
+      </c>
+      <c r="J2515" s="5">
+        <v>46217.374305555553</v>
+      </c>
+      <c r="K2515">
+        <v>8</v>
+      </c>
+      <c r="L2515">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2516" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2516">
+        <v>35095819</v>
+      </c>
+      <c r="B2516" s="5">
+        <v>46235</v>
+      </c>
+      <c r="C2516" t="s">
+        <v>23</v>
+      </c>
+      <c r="D2516" s="5">
+        <v>43708</v>
+      </c>
+      <c r="E2516" t="s">
+        <v>149</v>
+      </c>
+      <c r="F2516" t="s">
+        <v>31</v>
+      </c>
+      <c r="G2516" t="s">
+        <v>40</v>
+      </c>
+      <c r="H2516" t="s">
+        <v>41</v>
+      </c>
+      <c r="I2516" t="s">
+        <v>88</v>
+      </c>
+      <c r="J2516" s="5">
+        <v>46213.463888888888</v>
+      </c>
+      <c r="K2516">
+        <v>8</v>
+      </c>
+      <c r="L2516">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2517" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2517">
+        <v>45174307</v>
+      </c>
+      <c r="B2517" s="5">
+        <v>46243</v>
+      </c>
+      <c r="C2517" t="s">
+        <v>23</v>
+      </c>
+      <c r="D2517" s="5">
+        <v>43899</v>
+      </c>
+      <c r="E2517" t="s">
+        <v>149</v>
+      </c>
+      <c r="F2517" t="s">
+        <v>31</v>
+      </c>
+      <c r="G2517" t="s">
+        <v>32</v>
+      </c>
+      <c r="H2517" t="s">
+        <v>37</v>
+      </c>
+      <c r="I2517" t="s">
+        <v>140</v>
+      </c>
+      <c r="J2517" s="5">
+        <v>46224.378472222219</v>
+      </c>
+      <c r="K2517">
+        <v>8</v>
+      </c>
+      <c r="L2517">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2518" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2518">
+        <v>35111111</v>
+      </c>
+      <c r="B2518" s="5">
+        <v>46235</v>
+      </c>
+      <c r="C2518" t="s">
+        <v>62</v>
+      </c>
+      <c r="D2518" s="5">
+        <v>43799</v>
+      </c>
+      <c r="E2518" t="s">
+        <v>149</v>
+      </c>
+      <c r="F2518" t="s">
+        <v>31</v>
+      </c>
+      <c r="G2518" t="s">
+        <v>40</v>
+      </c>
+      <c r="H2518" t="s">
+        <v>41</v>
+      </c>
+      <c r="I2518" t="s">
+        <v>140</v>
+      </c>
+      <c r="J2518" s="5">
+        <v>46223.613888888889</v>
+      </c>
+      <c r="K2518">
+        <v>8</v>
+      </c>
+      <c r="L2518">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2519" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2519">
+        <v>1612308</v>
+      </c>
+      <c r="B2519" s="5">
+        <v>46235</v>
+      </c>
+      <c r="C2519" t="s">
+        <v>23</v>
+      </c>
+      <c r="D2519" s="5">
+        <v>43327</v>
+      </c>
+      <c r="E2519" t="s">
+        <v>149</v>
+      </c>
+      <c r="F2519" t="s">
+        <v>11</v>
+      </c>
+      <c r="G2519" t="s">
+        <v>38</v>
+      </c>
+      <c r="H2519" t="s">
+        <v>60</v>
+      </c>
+      <c r="I2519" t="s">
+        <v>140</v>
+      </c>
+      <c r="J2519" s="5">
+        <v>46225.701388888891</v>
+      </c>
+      <c r="K2519">
+        <v>8</v>
+      </c>
+      <c r="L2519">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2520" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2520">
+        <v>31200848</v>
+      </c>
+      <c r="B2520" s="5">
+        <v>46235</v>
+      </c>
+      <c r="C2520" t="s">
+        <v>103</v>
+      </c>
+      <c r="D2520" s="5">
+        <v>46171</v>
+      </c>
+      <c r="E2520" t="s">
+        <v>148</v>
+      </c>
+      <c r="F2520" t="s">
+        <v>31</v>
+      </c>
+      <c r="G2520" t="s">
+        <v>45</v>
+      </c>
+      <c r="H2520" t="s">
+        <v>90</v>
+      </c>
+      <c r="I2520" t="s">
+        <v>140</v>
+      </c>
+      <c r="J2520" s="5">
+        <v>46225.60833333333</v>
+      </c>
+      <c r="K2520">
+        <v>8</v>
+      </c>
+      <c r="L2520">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2521" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2521">
+        <v>30150580</v>
+      </c>
+      <c r="B2521" s="5">
+        <v>46236</v>
+      </c>
+      <c r="C2521" t="s">
+        <v>23</v>
+      </c>
+      <c r="D2521" s="5">
+        <v>45353</v>
+      </c>
+      <c r="E2521" t="s">
+        <v>147</v>
+      </c>
+      <c r="F2521" t="s">
+        <v>11</v>
+      </c>
+      <c r="G2521" t="s">
+        <v>49</v>
+      </c>
+      <c r="H2521" t="s">
+        <v>50</v>
+      </c>
+      <c r="I2521" t="s">
+        <v>42</v>
+      </c>
+      <c r="J2521" s="5">
+        <v>46209.410416666666</v>
+      </c>
+      <c r="K2521">
+        <v>8</v>
+      </c>
+      <c r="L2521">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2522" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2522">
+        <v>31126307</v>
+      </c>
+      <c r="B2522" s="5">
+        <v>46237</v>
+      </c>
+      <c r="C2522" t="s">
+        <v>23</v>
+      </c>
+      <c r="D2522" s="5">
+        <v>44898</v>
+      </c>
+      <c r="E2522" t="s">
+        <v>149</v>
+      </c>
+      <c r="F2522" t="s">
+        <v>31</v>
+      </c>
+      <c r="G2522" t="s">
+        <v>45</v>
+      </c>
+      <c r="H2522" t="s">
+        <v>76</v>
+      </c>
+      <c r="I2522" t="s">
+        <v>27</v>
+      </c>
+      <c r="J2522" s="5">
+        <v>46218.424305555556</v>
+      </c>
+      <c r="K2522">
+        <v>8</v>
+      </c>
+      <c r="L2522">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2523" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2523">
+        <v>50162177</v>
+      </c>
+      <c r="B2523" s="5">
+        <v>46244</v>
+      </c>
+      <c r="C2523" t="s">
+        <v>23</v>
+      </c>
+      <c r="D2523" s="5">
+        <v>45545</v>
+      </c>
+      <c r="E2523" t="s">
+        <v>150</v>
+      </c>
+      <c r="F2523" t="s">
+        <v>11</v>
+      </c>
+      <c r="G2523" t="s">
+        <v>12</v>
+      </c>
+      <c r="H2523" t="s">
+        <v>13</v>
+      </c>
+      <c r="I2523" t="s">
+        <v>27</v>
+      </c>
+      <c r="J2523" s="5">
+        <v>46212.481944444444</v>
+      </c>
+      <c r="K2523">
+        <v>8</v>
+      </c>
+      <c r="L2523">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2524" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2524">
+        <v>2020505</v>
+      </c>
+      <c r="B2524" s="5">
+        <v>46249</v>
+      </c>
+      <c r="C2524" t="s">
+        <v>62</v>
+      </c>
+      <c r="D2524" s="5">
+        <v>44484</v>
+      </c>
+      <c r="E2524" t="s">
+        <v>149</v>
+      </c>
+      <c r="F2524" t="s">
+        <v>11</v>
+      </c>
+      <c r="G2524" t="s">
+        <v>28</v>
+      </c>
+      <c r="H2524" t="s">
+        <v>48</v>
+      </c>
+      <c r="I2524" t="s">
+        <v>39</v>
+      </c>
+      <c r="J2524" s="5">
+        <v>46231.48333333333</v>
+      </c>
+      <c r="K2524">
+        <v>8</v>
+      </c>
+      <c r="L2524">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2525" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2525">
+        <v>35164976</v>
+      </c>
+      <c r="B2525" s="5">
+        <v>46240</v>
+      </c>
+      <c r="C2525" t="s">
+        <v>62</v>
+      </c>
+      <c r="D2525" s="5">
+        <v>44233</v>
+      </c>
+      <c r="E2525" t="s">
+        <v>149</v>
+      </c>
+      <c r="F2525" t="s">
+        <v>31</v>
+      </c>
+      <c r="G2525" t="s">
+        <v>40</v>
+      </c>
+      <c r="H2525" t="s">
+        <v>41</v>
+      </c>
+      <c r="I2525" t="s">
+        <v>14</v>
+      </c>
+      <c r="J2525" s="5">
+        <v>46218.478472222225</v>
+      </c>
+      <c r="K2525">
+        <v>8</v>
+      </c>
+      <c r="L2525">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2526" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2526">
+        <v>2117937</v>
+      </c>
+      <c r="B2526" s="5">
+        <v>46248</v>
+      </c>
+      <c r="C2526" t="s">
+        <v>23</v>
+      </c>
+      <c r="D2526" s="5">
+        <v>45305</v>
+      </c>
+      <c r="E2526" t="s">
+        <v>147</v>
+      </c>
+      <c r="F2526" t="s">
+        <v>11</v>
+      </c>
+      <c r="G2526" t="s">
+        <v>28</v>
+      </c>
+      <c r="H2526" t="s">
+        <v>48</v>
+      </c>
+      <c r="I2526" t="s">
+        <v>14</v>
+      </c>
+      <c r="J2526" s="5">
+        <v>46219.498611111114</v>
+      </c>
+      <c r="K2526">
+        <v>8</v>
+      </c>
+      <c r="L2526">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2527" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2527">
+        <v>20080432</v>
+      </c>
+      <c r="B2527" s="5">
+        <v>46235</v>
+      </c>
+      <c r="C2527" t="s">
+        <v>23</v>
+      </c>
+      <c r="D2527" s="5">
+        <v>44166</v>
+      </c>
+      <c r="E2527" t="s">
+        <v>149</v>
+      </c>
+      <c r="F2527" t="s">
+        <v>16</v>
+      </c>
+      <c r="G2527" t="s">
+        <v>20</v>
+      </c>
+      <c r="H2527" t="s">
+        <v>57</v>
+      </c>
+      <c r="I2527" t="s">
+        <v>14</v>
+      </c>
+      <c r="J2527" s="5">
+        <v>46231.418749999997</v>
+      </c>
+      <c r="K2527">
+        <v>8</v>
+      </c>
+      <c r="L2527">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2528" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2528">
+        <v>33009533</v>
+      </c>
+      <c r="B2528" s="5">
+        <v>46239</v>
+      </c>
+      <c r="C2528" t="s">
+        <v>142</v>
+      </c>
+      <c r="D2528" s="5">
+        <v>44809</v>
+      </c>
+      <c r="E2528" t="s">
+        <v>149</v>
+      </c>
+      <c r="F2528" t="s">
+        <v>31</v>
+      </c>
+      <c r="G2528" t="s">
+        <v>43</v>
+      </c>
+      <c r="H2528" t="s">
+        <v>74</v>
+      </c>
+      <c r="I2528" t="s">
+        <v>14</v>
+      </c>
+      <c r="J2528" s="5">
+        <v>46225.677083333336</v>
+      </c>
+      <c r="K2528">
+        <v>8</v>
+      </c>
+      <c r="L2528">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2529" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2529">
+        <v>41007577</v>
+      </c>
+      <c r="B2529" s="5">
+        <v>46252</v>
+      </c>
+      <c r="C2529" t="s">
+        <v>62</v>
+      </c>
+      <c r="D2529" s="5">
+        <v>45979</v>
+      </c>
+      <c r="E2529" t="s">
+        <v>152</v>
+      </c>
+      <c r="F2529" t="s">
+        <v>31</v>
+      </c>
+      <c r="G2529" t="s">
+        <v>69</v>
+      </c>
+      <c r="H2529" t="s">
+        <v>135</v>
+      </c>
+      <c r="I2529" t="s">
+        <v>51</v>
+      </c>
+      <c r="J2529" s="5">
+        <v>46234.426388888889</v>
+      </c>
+      <c r="K2529">
+        <v>8</v>
+      </c>
+      <c r="L2529">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2530" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2530">
+        <v>2124751</v>
+      </c>
+      <c r="B2530" s="5">
+        <v>46236</v>
+      </c>
+      <c r="C2530" t="s">
+        <v>62</v>
+      </c>
+      <c r="D2530" s="5">
+        <v>45384</v>
+      </c>
+      <c r="E2530" t="s">
+        <v>147</v>
+      </c>
+      <c r="F2530" t="s">
+        <v>11</v>
+      </c>
+      <c r="G2530" t="s">
+        <v>28</v>
+      </c>
+      <c r="H2530" t="s">
+        <v>34</v>
+      </c>
+      <c r="I2530" t="s">
+        <v>51</v>
+      </c>
+      <c r="J2530" s="5">
+        <v>46220.43472222222</v>
+      </c>
+      <c r="K2530">
+        <v>8</v>
+      </c>
+      <c r="L2530">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2531" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2531">
+        <v>20042800</v>
+      </c>
+      <c r="B2531" s="5">
+        <v>46235</v>
+      </c>
+      <c r="C2531" t="s">
+        <v>23</v>
+      </c>
+      <c r="D2531" s="5">
+        <v>43860</v>
+      </c>
+      <c r="E2531" t="s">
+        <v>149</v>
+      </c>
+      <c r="F2531" t="s">
+        <v>16</v>
+      </c>
+      <c r="G2531" t="s">
+        <v>20</v>
+      </c>
+      <c r="H2531" t="s">
+        <v>57</v>
+      </c>
+      <c r="I2531" t="s">
+        <v>51</v>
+      </c>
+      <c r="J2531" s="5">
+        <v>46217.386805555558</v>
+      </c>
+      <c r="K2531">
+        <v>8</v>
+      </c>
+      <c r="L2531">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2532" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2532">
+        <v>21108797</v>
+      </c>
+      <c r="B2532" s="5">
+        <v>46245</v>
+      </c>
+      <c r="C2532" t="s">
+        <v>23</v>
+      </c>
+      <c r="D2532" s="5">
+        <v>45333</v>
+      </c>
+      <c r="E2532" t="s">
+        <v>147</v>
+      </c>
+      <c r="F2532" t="s">
+        <v>16</v>
+      </c>
+      <c r="G2532" t="s">
+        <v>54</v>
+      </c>
+      <c r="H2532" t="s">
+        <v>78</v>
+      </c>
+      <c r="I2532" t="s">
+        <v>51</v>
+      </c>
+      <c r="J2532" s="5">
+        <v>46212.491666666669</v>
+      </c>
+      <c r="K2532">
+        <v>8</v>
+      </c>
+      <c r="L2532">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2533" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2533">
+        <v>50110482</v>
+      </c>
+      <c r="B2533" s="5">
+        <v>46243</v>
+      </c>
+      <c r="C2533" t="s">
+        <v>23</v>
+      </c>
+      <c r="D2533" s="5">
+        <v>44325</v>
+      </c>
+      <c r="E2533" t="s">
+        <v>149</v>
+      </c>
+      <c r="F2533" t="s">
+        <v>11</v>
+      </c>
+      <c r="G2533" t="s">
+        <v>12</v>
+      </c>
+      <c r="H2533" t="s">
+        <v>13</v>
+      </c>
+      <c r="I2533" t="s">
+        <v>51</v>
+      </c>
+      <c r="J2533" s="5">
+        <v>46218.466666666667</v>
+      </c>
+      <c r="K2533">
+        <v>8</v>
+      </c>
+      <c r="L2533">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2534" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2534">
+        <v>50164445</v>
+      </c>
+      <c r="B2534" s="5">
+        <v>46235</v>
+      </c>
+      <c r="C2534" t="s">
+        <v>85</v>
+      </c>
+      <c r="D2534" s="5">
+        <v>45594</v>
+      </c>
+      <c r="E2534" t="s">
+        <v>150</v>
+      </c>
+      <c r="F2534" t="s">
+        <v>11</v>
+      </c>
+      <c r="G2534" t="s">
+        <v>12</v>
+      </c>
+      <c r="H2534" t="s">
+        <v>13</v>
+      </c>
+      <c r="I2534" t="s">
+        <v>51</v>
+      </c>
+      <c r="J2534" s="5">
+        <v>46220.344444444447</v>
+      </c>
+      <c r="K2534">
+        <v>8</v>
+      </c>
+      <c r="L2534">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2535" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2535">
+        <v>1737212</v>
+      </c>
+      <c r="B2535" s="5">
+        <v>46243</v>
+      </c>
+      <c r="C2535" t="s">
+        <v>87</v>
+      </c>
+      <c r="D2535" s="5">
+        <v>45786</v>
+      </c>
+      <c r="E2535" t="s">
+        <v>150</v>
+      </c>
+      <c r="F2535" t="s">
+        <v>11</v>
+      </c>
+      <c r="G2535" t="s">
+        <v>28</v>
+      </c>
+      <c r="H2535" t="s">
+        <v>34</v>
+      </c>
+      <c r="I2535" t="s">
+        <v>30</v>
+      </c>
+      <c r="J2535" s="5">
+        <v>46218.463888888888</v>
+      </c>
+      <c r="K2535">
+        <v>8</v>
+      </c>
+      <c r="L2535">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2536" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2536">
+        <v>2121673</v>
+      </c>
+      <c r="B2536" s="5">
+        <v>46235</v>
+      </c>
+      <c r="C2536" t="s">
+        <v>23</v>
+      </c>
+      <c r="D2536" s="5">
+        <v>45352</v>
+      </c>
+      <c r="E2536" t="s">
+        <v>147</v>
+      </c>
+      <c r="F2536" t="s">
+        <v>11</v>
+      </c>
+      <c r="G2536" t="s">
+        <v>28</v>
+      </c>
+      <c r="H2536" t="s">
+        <v>34</v>
+      </c>
+      <c r="I2536" t="s">
+        <v>30</v>
+      </c>
+      <c r="J2536" s="5">
+        <v>46216.648611111108</v>
+      </c>
+      <c r="K2536">
+        <v>8</v>
+      </c>
+      <c r="L2536">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2537" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2537">
+        <v>31116071</v>
+      </c>
+      <c r="B2537" s="5">
+        <v>46250</v>
+      </c>
+      <c r="C2537" t="s">
+        <v>62</v>
+      </c>
+      <c r="D2537" s="5">
+        <v>44697</v>
+      </c>
+      <c r="E2537" t="s">
+        <v>149</v>
+      </c>
+      <c r="F2537" t="s">
+        <v>31</v>
+      </c>
+      <c r="G2537" t="s">
+        <v>45</v>
+      </c>
+      <c r="H2537" t="s">
+        <v>75</v>
+      </c>
+      <c r="I2537" t="s">
+        <v>30</v>
+      </c>
+      <c r="J2537" s="5">
+        <v>46223.394444444442</v>
+      </c>
+      <c r="K2537">
+        <v>8</v>
+      </c>
+      <c r="L2537">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2538" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2538">
+        <v>50140037</v>
+      </c>
+      <c r="B2538" s="5">
+        <v>46243</v>
+      </c>
+      <c r="C2538" t="s">
+        <v>85</v>
+      </c>
+      <c r="D2538" s="5">
+        <v>44966</v>
+      </c>
+      <c r="E2538" t="s">
+        <v>149</v>
+      </c>
+      <c r="F2538" t="s">
+        <v>11</v>
+      </c>
+      <c r="G2538" t="s">
+        <v>12</v>
+      </c>
+      <c r="H2538" t="s">
+        <v>13</v>
+      </c>
+      <c r="I2538" t="s">
+        <v>30</v>
+      </c>
+      <c r="J2538" s="5">
+        <v>46218.413194444445</v>
+      </c>
+      <c r="K2538">
+        <v>8</v>
+      </c>
+      <c r="L2538">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2539" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2539">
+        <v>50143834</v>
+      </c>
+      <c r="B2539" s="5">
+        <v>46244</v>
+      </c>
+      <c r="C2539" t="s">
+        <v>62</v>
+      </c>
+      <c r="D2539" s="5">
+        <v>45026</v>
+      </c>
+      <c r="E2539" t="s">
+        <v>149</v>
+      </c>
+      <c r="F2539" t="s">
+        <v>11</v>
+      </c>
+      <c r="G2539" t="s">
+        <v>12</v>
+      </c>
+      <c r="H2539" t="s">
+        <v>13</v>
+      </c>
+      <c r="I2539" t="s">
+        <v>30</v>
+      </c>
+      <c r="J2539" s="5">
+        <v>46231.601388888892</v>
+      </c>
+      <c r="K2539">
+        <v>8</v>
+      </c>
+      <c r="L2539">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2540" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2540">
+        <v>31058936</v>
+      </c>
+      <c r="B2540" s="5">
+        <v>46235</v>
+      </c>
+      <c r="C2540" t="s">
+        <v>62</v>
+      </c>
+      <c r="D2540" s="5">
+        <v>43951</v>
+      </c>
+      <c r="E2540" t="s">
+        <v>149</v>
+      </c>
+      <c r="F2540" t="s">
+        <v>31</v>
+      </c>
+      <c r="G2540" t="s">
+        <v>45</v>
+      </c>
+      <c r="H2540" t="s">
+        <v>75</v>
+      </c>
+      <c r="I2540" t="s">
+        <v>36</v>
+      </c>
+      <c r="J2540" s="5">
+        <v>46219.428472222222</v>
+      </c>
+      <c r="K2540">
+        <v>8</v>
+      </c>
+      <c r="L2540">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2541" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2541">
+        <v>31110032</v>
+      </c>
+      <c r="B2541" s="5">
+        <v>46235</v>
+      </c>
+      <c r="C2541" t="s">
+        <v>23</v>
+      </c>
+      <c r="D2541" s="5">
+        <v>44560</v>
+      </c>
+      <c r="E2541" t="s">
+        <v>149</v>
+      </c>
+      <c r="F2541" t="s">
+        <v>31</v>
+      </c>
+      <c r="G2541" t="s">
+        <v>45</v>
+      </c>
+      <c r="H2541" t="s">
+        <v>75</v>
+      </c>
+      <c r="I2541" t="s">
+        <v>36</v>
+      </c>
+      <c r="J2541" s="5">
+        <v>46209.320833333331</v>
+      </c>
+      <c r="K2541">
+        <v>8</v>
+      </c>
+      <c r="L2541">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2542" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2542">
+        <v>35216214</v>
+      </c>
+      <c r="B2542" s="5">
+        <v>46243</v>
+      </c>
+      <c r="C2542" t="s">
+        <v>62</v>
+      </c>
+      <c r="D2542" s="5">
+        <v>45697</v>
+      </c>
+      <c r="E2542" t="s">
+        <v>150</v>
+      </c>
+      <c r="F2542" t="s">
+        <v>31</v>
+      </c>
+      <c r="G2542" t="s">
+        <v>40</v>
+      </c>
+      <c r="H2542" t="s">
+        <v>41</v>
+      </c>
+      <c r="I2542" t="s">
+        <v>19</v>
+      </c>
+      <c r="J2542" s="5">
+        <v>46214.481249999997</v>
+      </c>
+      <c r="K2542">
+        <v>8</v>
+      </c>
+      <c r="L2542">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2543" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2543">
+        <v>2151786</v>
+      </c>
+      <c r="B2543" s="5">
+        <v>46235</v>
+      </c>
+      <c r="C2543" t="s">
+        <v>144</v>
+      </c>
+      <c r="D2543" s="5">
+        <v>45686</v>
+      </c>
+      <c r="E2543" t="s">
+        <v>150</v>
+      </c>
+      <c r="F2543" t="s">
+        <v>11</v>
+      </c>
+      <c r="G2543" t="s">
+        <v>38</v>
+      </c>
+      <c r="H2543" t="s">
+        <v>60</v>
+      </c>
+      <c r="I2543" t="s">
+        <v>19</v>
+      </c>
+      <c r="J2543" s="5">
+        <v>46234.38958333333</v>
+      </c>
+      <c r="K2543">
+        <v>8</v>
+      </c>
+      <c r="L2543">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2544" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2544">
+        <v>31190238</v>
+      </c>
+      <c r="B2544" s="5">
+        <v>46244</v>
+      </c>
+      <c r="C2544" t="s">
+        <v>62</v>
+      </c>
+      <c r="D2544" s="5">
+        <v>46032</v>
+      </c>
+      <c r="E2544" t="s">
+        <v>151</v>
+      </c>
+      <c r="F2544" t="s">
+        <v>31</v>
+      </c>
+      <c r="G2544" t="s">
+        <v>45</v>
+      </c>
+      <c r="H2544" t="s">
+        <v>46</v>
+      </c>
+      <c r="I2544" t="s">
+        <v>19</v>
+      </c>
+      <c r="J2544" s="5">
+        <v>46216.498611111114</v>
+      </c>
+      <c r="K2544">
+        <v>8</v>
+      </c>
+      <c r="L2544">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2545" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2545">
+        <v>50103604</v>
+      </c>
+      <c r="B2545" s="5">
+        <v>46239</v>
+      </c>
+      <c r="C2545" t="s">
+        <v>23</v>
+      </c>
+      <c r="D2545" s="5">
+        <v>44079</v>
+      </c>
+      <c r="E2545" t="s">
+        <v>149</v>
+      </c>
+      <c r="F2545" t="s">
+        <v>11</v>
+      </c>
+      <c r="G2545" t="s">
+        <v>12</v>
+      </c>
+      <c r="H2545" t="s">
+        <v>13</v>
+      </c>
+      <c r="I2545" t="s">
+        <v>19</v>
+      </c>
+      <c r="J2545" s="5">
+        <v>46219.425000000003</v>
+      </c>
+      <c r="K2545">
+        <v>8</v>
+      </c>
+      <c r="L2545">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2546" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2546">
+        <v>20154400</v>
+      </c>
+      <c r="B2546" s="5">
+        <v>46241</v>
+      </c>
+      <c r="C2546" t="s">
+        <v>142</v>
+      </c>
+      <c r="D2546" s="5">
+        <v>45723</v>
+      </c>
+      <c r="E2546" t="s">
+        <v>150</v>
+      </c>
+      <c r="F2546" t="s">
+        <v>16</v>
+      </c>
+      <c r="G2546" t="s">
+        <v>20</v>
+      </c>
+      <c r="H2546" t="s">
+        <v>21</v>
+      </c>
+      <c r="I2546" t="s">
+        <v>47</v>
+      </c>
+      <c r="J2546" s="5">
+        <v>46227.397916666669</v>
+      </c>
+      <c r="K2546">
+        <v>8</v>
+      </c>
+      <c r="L2546">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2547" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2547">
+        <v>50161757</v>
+      </c>
+      <c r="B2547" s="5">
+        <v>46245</v>
+      </c>
+      <c r="C2547" t="s">
+        <v>142</v>
+      </c>
+      <c r="D2547" s="5">
+        <v>45515</v>
+      </c>
+      <c r="E2547" t="s">
+        <v>147</v>
+      </c>
+      <c r="F2547" t="s">
+        <v>11</v>
+      </c>
+      <c r="G2547" t="s">
+        <v>12</v>
+      </c>
+      <c r="H2547" t="s">
+        <v>24</v>
+      </c>
+      <c r="I2547" t="s">
+        <v>47</v>
+      </c>
+      <c r="J2547" s="5">
+        <v>46232.561805555553</v>
+      </c>
+      <c r="K2547">
+        <v>8</v>
+      </c>
+      <c r="L2547">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2548" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2548">
+        <v>31165238</v>
+      </c>
+      <c r="B2548" s="5">
+        <v>46249</v>
+      </c>
+      <c r="C2548" t="s">
+        <v>62</v>
+      </c>
+      <c r="D2548" s="5">
+        <v>46037</v>
+      </c>
+      <c r="E2548" t="s">
+        <v>151</v>
+      </c>
+      <c r="F2548" t="s">
+        <v>31</v>
+      </c>
+      <c r="G2548" t="s">
+        <v>45</v>
+      </c>
+      <c r="H2548" t="s">
+        <v>75</v>
+      </c>
+      <c r="I2548" t="s">
+        <v>141</v>
+      </c>
+      <c r="J2548" s="5">
+        <v>46218.428472222222</v>
+      </c>
+      <c r="K2548">
+        <v>8</v>
+      </c>
+      <c r="L2548">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2549" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2549">
+        <v>1803394</v>
+      </c>
+      <c r="B2549" s="5">
+        <v>46249</v>
+      </c>
+      <c r="C2549" t="s">
+        <v>23</v>
+      </c>
+      <c r="D2549" s="5">
+        <v>43814</v>
+      </c>
+      <c r="E2549" t="s">
+        <v>149</v>
+      </c>
+      <c r="F2549" t="s">
+        <v>11</v>
+      </c>
+      <c r="G2549" t="s">
+        <v>28</v>
+      </c>
+      <c r="H2549" t="s">
+        <v>48</v>
+      </c>
+      <c r="I2549" t="s">
+        <v>22</v>
+      </c>
+      <c r="J2549" s="5">
+        <v>46226.474305555559</v>
+      </c>
+      <c r="K2549">
+        <v>8</v>
+      </c>
+      <c r="L2549">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2550" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2550">
+        <v>21118758</v>
+      </c>
+      <c r="B2550" s="5">
+        <v>46236</v>
+      </c>
+      <c r="C2550" t="s">
+        <v>23</v>
+      </c>
+      <c r="D2550" s="5">
+        <v>45567</v>
+      </c>
+      <c r="E2550" t="s">
+        <v>150</v>
+      </c>
+      <c r="F2550" t="s">
+        <v>16</v>
+      </c>
+      <c r="G2550" t="s">
+        <v>54</v>
+      </c>
+      <c r="H2550" t="s">
+        <v>55</v>
+      </c>
+      <c r="I2550" t="s">
+        <v>22</v>
+      </c>
+      <c r="J2550" s="5">
+        <v>46223.351388888892</v>
+      </c>
+      <c r="K2550">
+        <v>8</v>
+      </c>
+      <c r="L2550">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2551" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2551">
+        <v>30131652</v>
+      </c>
+      <c r="B2551" s="5">
+        <v>46235</v>
+      </c>
+      <c r="C2551" t="s">
+        <v>62</v>
+      </c>
+      <c r="D2551" s="5">
+        <v>44863</v>
+      </c>
+      <c r="E2551" t="s">
+        <v>149</v>
+      </c>
+      <c r="F2551" t="s">
+        <v>11</v>
+      </c>
+      <c r="G2551" t="s">
+        <v>49</v>
+      </c>
+      <c r="H2551" t="s">
+        <v>50</v>
+      </c>
+      <c r="I2551" t="s">
+        <v>53</v>
+      </c>
+      <c r="J2551" s="5">
+        <v>46226.407638888886</v>
+      </c>
+      <c r="K2551">
+        <v>8</v>
+      </c>
+      <c r="L2551">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2552" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2552">
+        <v>2094899</v>
+      </c>
+      <c r="B2552" s="5">
+        <v>46237</v>
+      </c>
+      <c r="C2552" t="s">
+        <v>23</v>
+      </c>
+      <c r="D2552" s="5">
+        <v>45110</v>
+      </c>
+      <c r="E2552" t="s">
+        <v>149</v>
+      </c>
+      <c r="F2552" t="s">
+        <v>11</v>
+      </c>
+      <c r="G2552" t="s">
+        <v>38</v>
+      </c>
+      <c r="H2552" t="s">
+        <v>29</v>
+      </c>
+      <c r="I2552" t="s">
+        <v>53</v>
+      </c>
+      <c r="J2552" s="5">
+        <v>46225.413194444445</v>
+      </c>
+      <c r="K2552">
+        <v>8</v>
+      </c>
+      <c r="L2552">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2553" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2553">
+        <v>50159265</v>
+      </c>
+      <c r="B2553" s="5">
+        <v>46235</v>
+      </c>
+      <c r="C2553" t="s">
+        <v>85</v>
+      </c>
+      <c r="D2553" s="5">
+        <v>45442</v>
+      </c>
+      <c r="E2553" t="s">
+        <v>147</v>
+      </c>
+      <c r="F2553" t="s">
+        <v>11</v>
+      </c>
+      <c r="G2553" t="s">
+        <v>12</v>
+      </c>
+      <c r="H2553" t="s">
+        <v>13</v>
+      </c>
+      <c r="I2553" t="s">
+        <v>53</v>
+      </c>
+      <c r="J2553" s="5">
+        <v>46230.462500000001</v>
+      </c>
+      <c r="K2553">
+        <v>8</v>
+      </c>
+      <c r="L2553">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2554" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2554">
+        <v>35201826</v>
+      </c>
+      <c r="B2554" s="5">
+        <v>46235</v>
+      </c>
+      <c r="C2554" t="s">
+        <v>62</v>
+      </c>
+      <c r="D2554" s="5">
+        <v>45352</v>
+      </c>
+      <c r="E2554" t="s">
+        <v>147</v>
+      </c>
+      <c r="F2554" t="s">
+        <v>31</v>
+      </c>
+      <c r="G2554" t="s">
+        <v>40</v>
+      </c>
+      <c r="H2554" t="s">
+        <v>41</v>
+      </c>
+      <c r="I2554" t="s">
+        <v>56</v>
+      </c>
+      <c r="J2554" s="5">
+        <v>46219.463888888888</v>
+      </c>
+      <c r="K2554">
+        <v>8</v>
+      </c>
+      <c r="L2554">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2555" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2555">
+        <v>1465954</v>
+      </c>
+      <c r="B2555" s="5">
+        <v>46235</v>
+      </c>
+      <c r="C2555" t="s">
+        <v>23</v>
+      </c>
+      <c r="D2555" s="5">
+        <v>42542</v>
+      </c>
+      <c r="E2555" t="s">
+        <v>149</v>
+      </c>
+      <c r="F2555" t="s">
+        <v>11</v>
+      </c>
+      <c r="G2555" t="s">
+        <v>38</v>
+      </c>
+      <c r="H2555" t="s">
+        <v>29</v>
+      </c>
+      <c r="I2555" t="s">
+        <v>56</v>
+      </c>
+      <c r="J2555" s="5">
+        <v>46216.469444444447</v>
+      </c>
+      <c r="K2555">
+        <v>8</v>
+      </c>
+      <c r="L2555">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2556" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2556">
+        <v>31097198</v>
+      </c>
+      <c r="B2556" s="5">
+        <v>46238</v>
+      </c>
+      <c r="C2556" t="s">
+        <v>23</v>
+      </c>
+      <c r="D2556" s="5">
+        <v>44169</v>
+      </c>
+      <c r="E2556" t="s">
+        <v>149</v>
+      </c>
+      <c r="F2556" t="s">
+        <v>31</v>
+      </c>
+      <c r="G2556" t="s">
+        <v>45</v>
+      </c>
+      <c r="H2556" t="s">
+        <v>46</v>
+      </c>
+      <c r="I2556" t="s">
+        <v>56</v>
+      </c>
+      <c r="J2556" s="5">
+        <v>46210.436111111114</v>
+      </c>
+      <c r="K2556">
+        <v>8</v>
+      </c>
+      <c r="L2556">
+        <v>2026</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L1" xr:uid="{129E8E4B-63D9-47F0-9896-1DD628D404DA}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A1433:P1936">
     <sortCondition ref="I1433:I1936"/>
   </sortState>
